--- a/UAT_Excel_Reports/By Product Daily_UAT.xlsx
+++ b/UAT_Excel_Reports/By Product Daily_UAT.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F316"/>
+  <dimension ref="A1:F378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -496,39 +496,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>B.1</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Launch a Chromium browser instance in non-headless mode.</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>`playwright.chromium.launch(headless=False)`</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>--- BROWSER INITIALIZATION AND PAGE NAVIGATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>B.2</t>
+          <t>B.1</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Create a new browser context to isolate session data.</t>
+          <t>Launch a Chromium browser instance in non-headless mode.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>`browser.new_context()`</t>
+          <t>`playwright.chromium.launch(headless=False)`</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
@@ -538,17 +525,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>B.3</t>
+          <t>B.2</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Open a new page within the created browser context.</t>
+          <t>Create a new browser context to isolate session data.</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>`context.new_page()`</t>
+          <t>`browser.new_context()`</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
@@ -558,17 +545,17 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>B.4</t>
+          <t>B.3</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Navigate to the 'Executive Dashboard' in the demand planning application using the specified URL.</t>
+          <t>Open a new page within the created browser context.</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>`page.goto("https://stage.bbu.esp.antuit.ai/dp/demand-planning/executive-dashboard?workbookId=4&amp;tabIndex=3")`</t>
+          <t>`context.new_page()`</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
@@ -578,17 +565,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C.1</t>
+          <t>B.4</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Product Total columns (0)' text to open the configuration panel for product total columns.</t>
+          <t>Navigate to the 'Executive Dashboard' in the demand planning application using the specified URL.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Product Total columns (0)").click()`</t>
+          <t>`page.goto("https://stage.bbu.esp.antuit.ai/dp/demand-planning/executive-dashboard?workbookId=4&amp;tabIndex=3")`</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
@@ -596,39 +583,26 @@
       <c r="F7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>C.2</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Repeat the click on 'Product Total columns (0)' to ensure the panel is opened (possibly redundant or for stability).</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Product Total columns (0)").click()`</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>--- PRODUCT TOTAL COLUMNS CONFIGURATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C.3</t>
+          <t>C.1</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Product Total' text to select or focus on the product total section.</t>
+          <t>Click on the 'Product Total columns (0)' text to open the configuration panel for product total columns.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Product Total").click()`</t>
+          <t>`page.get_by_text("Product Total columns (0)").click()`</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
@@ -638,17 +612,17 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>C.4</t>
+          <t>C.2</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Click on the button within the 'Product Total columns (0)' card component to proceed with further configuration.</t>
+          <t>Repeat the click on 'Product Total columns (0)' to ensure the panel is opened (possibly redundant or for stability).</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Product Total columns (0)").get_by_role("button").click()`</t>
+          <t>`page.get_by_text("Product Total columns (0)").click()`</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr"/>
@@ -658,17 +632,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>D.1</t>
+          <t>C.3</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Filter Columns Input' textbox to focus on the input field for filtering columns.</t>
+          <t>Click on the 'Product Total' text to select or focus on the product total section.</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
+          <t>`page.get_by_text("Product Total").click()`</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
@@ -678,17 +652,17 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>D.2</t>
+          <t>C.4</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns initially.</t>
+          <t>Click on the button within the 'Product Total columns (0)' card component to proceed with further configuration.</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Product Total columns (0)").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr"/>
@@ -696,39 +670,26 @@
       <c r="F12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>D.3</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Filter Columns Input' textbox again to ensure it is focused for input.</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>--- FILTER COLUMNS INPUT INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>D.4</t>
+          <t>D.1</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Fill the 'Filter Columns Input' textbox with the text 'system' to filter columns containing this keyword.</t>
+          <t>Click on the 'Filter Columns Input' textbox to focus on the input field for filtering columns.</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("system")`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
@@ -738,17 +699,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>D.5</t>
+          <t>D.2</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Press 'Enter' in the 'Filter Columns Input' textbox to apply the filter.</t>
+          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns initially.</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").press("Enter")`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr"/>
@@ -758,17 +719,17 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>E.1</t>
+          <t>D.3</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Click on the first column in the filtered list to select it.</t>
+          <t>Click on the 'Filter Columns Input' textbox again to ensure it is focused for input.</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-column-select-column").first.click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr"/>
@@ -778,17 +739,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>E.2</t>
+          <t>D.4</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the checkbox for 'System Forecast Base (Plan' to deselect this column.</t>
+          <t>Fill the 'Filter Columns Input' textbox with the text 'system' to filter columns containing this keyword.</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan").get_by_label("Press SPACE to toggle").uncheck()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("system")`</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr"/>
@@ -798,17 +759,17 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>E.3</t>
+          <t>D.5</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Filter Columns Input' textbox to clear or modify the filter.</t>
+          <t>Press 'Enter' in the 'Filter Columns Input' textbox to apply the filter.</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").press("Enter")`</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr"/>
@@ -816,39 +777,26 @@
       <c r="F18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>E.4</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Clear the 'Filter Columns Input' textbox by filling it with an empty string.</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("")`</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>--- COLUMN SELECTION AND DESELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>E.5</t>
+          <t>E.1</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Press 'Enter' in the 'Filter Columns Input' textbox to reset the filter.</t>
+          <t>Click on the first column in the filtered list to select it.</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").press("Enter")`</t>
+          <t>`page.locator(".ag-column-select-column").first.click()`</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
@@ -858,17 +806,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>E.6</t>
+          <t>E.2</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'System Forecast Total (Plan Week) Column' tree item to select it.</t>
+          <t>Uncheck the checkbox for 'System Forecast Base (Plan' to deselect this column.</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan Week) Column").click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan").get_by_label("Press SPACE to toggle").uncheck()`</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
@@ -878,17 +826,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>E.7</t>
+          <t>E.3</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the checkbox for 'System Forecast Base (Plan' again to ensure it is deselected.</t>
+          <t>Click on the 'Filter Columns Input' textbox to clear or modify the filter.</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan").get_by_label("Press SPACE to toggle").uncheck()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
@@ -898,17 +846,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>F.1</t>
+          <t>E.4</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'System Forecast Promotion (' label to select this column.</t>
+          <t>Clear the 'Filter Columns Input' textbox by filling it with an empty string.</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("System Forecast Promotion (").get_by_text("System Forecast Promotion (").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("")`</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
@@ -918,17 +866,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>F.2</t>
+          <t>E.5</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'System Forecast Total (Plan+1' label to select this column.</t>
+          <t>Press 'Enter' in the 'Filter Columns Input' textbox to reset the filter.</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("System Forecast Total (Plan+1").get_by_text("System Forecast Total (Plan+1").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").press("Enter")`</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
@@ -938,17 +886,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>F.3</t>
+          <t>E.6</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'System Forecast Base (Plan+1' label to select this column.</t>
+          <t>Click on the 'System Forecast Total (Plan Week) Column' tree item to select it.</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("System Forecast Base (Plan+1").get_by_text("System Forecast Base (Plan+1").click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan Week) Column").click()`</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
@@ -958,17 +906,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>F.4</t>
+          <t>E.7</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'System Forecast Promotion (Plan+1 Week) Column' label to select this column.</t>
+          <t>Uncheck the checkbox for 'System Forecast Base (Plan' again to ensure it is deselected.</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("System Forecast Promotion (Plan+1 Week) Column").get_by_text("System Forecast Promotion (").click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan").get_by_label("Press SPACE to toggle").uncheck()`</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr"/>
@@ -976,39 +924,26 @@
       <c r="F26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>F.5</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Click on the '6 Week Gross Units Average' label to select this column.</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_label("6 Week Gross Units Average").get_by_text("Week Gross Units Average").click()`</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>--- SPECIFIC COLUMN SELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>F.6</t>
+          <t>F.1</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Click on the '6 Week Aged Net Units Average Column' label to select this column.</t>
+          <t>Click on the 'System Forecast Promotion (' label to select this column.</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("6 Week Aged Net Units Average Column", exact=True).get_by_text("Week Aged Net Units Average").click()`</t>
+          <t>`page.get_by_label("System Forecast Promotion (").get_by_text("System Forecast Promotion (").click()`</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
@@ -1018,17 +953,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>F.7</t>
+          <t>F.2</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'LY 6 Week Aged Net Units' label to select this column.</t>
+          <t>Click on the 'System Forecast Total (Plan+1' label to select this column.</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("LY 6 Week Aged Net Units").get_by_text("LY 6 Week Aged Net Units").click()`</t>
+          <t>`page.get_by_label("System Forecast Total (Plan+1").get_by_text("System Forecast Total (Plan+1").click()`</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
@@ -1038,17 +973,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>G.1</t>
+          <t>F.3</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'LY 6 Week Scan Units Average' label to select this column.</t>
+          <t>Click on the 'System Forecast Base (Plan+1' label to select this column.</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("LY 6 Week Scan Units Average").get_by_text("LY 6 Week Scan Units Average").click()`</t>
+          <t>`page.get_by_label("System Forecast Base (Plan+1").get_by_text("System Forecast Base (Plan+1").click()`</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
@@ -1058,17 +993,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>G.2</t>
+          <t>F.4</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Click on the '6 Week Scan Units Average Column' label to select this column.</t>
+          <t>Click on the 'System Forecast Promotion (Plan+1 Week) Column' label to select this column.</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("6 Week Scan Units Average Column", exact=True).get_by_text("Week Scan Units Average").click()`</t>
+          <t>`page.get_by_label("System Forecast Promotion (Plan+1 Week) Column").get_by_text("System Forecast Promotion (").click()`</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
@@ -1078,17 +1013,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>G.3</t>
+          <t>F.5</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Click on the '% Change 6 Week Aged Net' label to select this column.</t>
+          <t>Click on the '6 Week Gross Units Average' label to select this column.</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("% Change 6 Week Aged Net").get_by_text("% Change 6 Week Aged Net").click()`</t>
+          <t>`page.get_by_label("6 Week Gross Units Average").get_by_text("Week Gross Units Average").click()`</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr"/>
@@ -1098,17 +1033,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>G.4</t>
+          <t>F.6</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Click on the '% Change 6 Week Scan Units' label to select this column.</t>
+          <t>Click on the '6 Week Aged Net Units Average Column' label to select this column.</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("% Change 6 Week Scan Units").get_by_text("% Change 6 Week Scan Units").click()`</t>
+          <t>`page.get_by_label("6 Week Aged Net Units Average Column", exact=True).get_by_text("Week Aged Net Units Average").click()`</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
@@ -1118,17 +1053,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>G.5</t>
+          <t>F.7</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Freshness (6 Week Average)' label to select this column.</t>
+          <t>Click on the 'LY 6 Week Aged Net Units' label to select this column.</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("Freshness (6 Week Average)").get_by_text("Freshness (6 Week Average)").click()`</t>
+          <t>`page.get_by_label("LY 6 Week Aged Net Units").get_by_text("LY 6 Week Aged Net Units").click()`</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
@@ -1136,39 +1071,26 @@
       <c r="F34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>G.6</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Click on the '6 Week Aged Returns Units' label to select this column.</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_label("6 Week Aged Returns Units").get_by_text("6 Week Aged Returns Units").click()`</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>--- COLUMN SELECTION AND VISIBILITY TOGGLES ---</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>G.7</t>
+          <t>G.1</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible again.</t>
+          <t>Click on the 'LY 6 Week Scan Units Average' label to select this column.</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+          <t>`page.get_by_label("LY 6 Week Scan Units Average").get_by_text("LY 6 Week Scan Units Average").click()`</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
@@ -1178,17 +1100,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>H.1</t>
+          <t>G.2</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Product Total columns (0)' button to open the column selection menu.</t>
+          <t>Click on the '6 Week Scan Units Average Column' label to select this column.</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Product Total columns (0)").get_by_role("button").click()`</t>
+          <t>`page.get_by_label("6 Week Scan Units Average Column", exact=True).get_by_text("Week Scan Units Average").click()`</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
@@ -1198,17 +1120,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>H.2</t>
+          <t>G.3</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Click on the download icon to initiate the download of the selected data.</t>
+          <t>Click on the '% Change 6 Week Aged Net' label to select this column.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".icon-color-toolbar-active.zeb-download-underline").first.click()`</t>
+          <t>`page.get_by_label("% Change 6 Week Aged Net").get_by_text("% Change 6 Week Aged Net").click()`</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr"/>
@@ -1218,17 +1140,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>I.1</t>
+          <t>G.4</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Click on the informational message that begins with 'Please note that a maximum of' to acknowledge it.</t>
+          <t>Click on the '% Change 6 Week Scan Units' label to select this column.</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Please note that a maximum of").click()`</t>
+          <t>`page.get_by_label("% Change 6 Week Scan Units").get_by_text("% Change 6 Week Scan Units").click()`</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
@@ -1238,17 +1160,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>I.2</t>
+          <t>G.5</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Click on the adjustments icon to open the settings menu.</t>
+          <t>Click on the 'Freshness (6 Week Average)' label to select this column.</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".pointer.zeb-adjustments").first.click()`</t>
+          <t>`page.get_by_label("Freshness (6 Week Average)").get_by_text("Freshness (6 Week Average)").click()`</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
@@ -1258,17 +1180,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>I.3</t>
+          <t>G.6</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Save Preference' button to save the current column visibility settings.</t>
+          <t>Click on the '6 Week Aged Returns Units' label to select this column.</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Save Preference").click()`</t>
+          <t>`page.get_by_label("6 Week Aged Returns Units").get_by_text("6 Week Aged Returns Units").click()`</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
@@ -1278,17 +1200,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>I.4</t>
+          <t>G.7</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Click on the adjustments icon again to reopen the settings menu.</t>
+          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible again.</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".pointer.zeb-adjustments").first.click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
@@ -1296,39 +1218,26 @@
       <c r="F42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>I.5</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Reset Preference' button to reset the column visibility settings to their default state.</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Reset Preference").click()`</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>--- DOWNLOAD DATA PROCESS ---</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>J.1</t>
+          <t>H.1</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Click on the horizontal scroll container to ensure the view is scrolled to the appropriate section.</t>
+          <t>Click on the 'Product Total columns (0)' button to open the column selection menu.</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-body-horizontal-scroll-container").first.click()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Product Total columns (0)").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
@@ -1338,17 +1247,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>J.2</t>
+          <t>H.2</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Products columns (0) TopBottom' button to open the column selection menu.</t>
+          <t>Click on the download icon to initiate the download of the selected data.</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Products columns (0) TopBottom").click()`</t>
+          <t>`page.locator(".icon-color-toolbar-active.zeb-download-underline").first.click()`</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
@@ -1356,39 +1265,26 @@
       <c r="F45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>J.3</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Products' section to focus on the product-related columns.</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Products").click()`</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>--- PREFERENCE MANAGEMENT ---</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>J.4</t>
+          <t>I.1</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Click on the button within the 'Products columns (0)' card to open the column configuration options.</t>
+          <t>Click on the informational message that begins with 'Please note that a maximum of' to acknowledge it.</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Products columns (0)").get_by_role("button").click()`</t>
+          <t>`page.get_by_text("Please note that a maximum of").click()`</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
@@ -1398,17 +1294,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>J.5</t>
+          <t>I.2</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Filter Columns Input' textbox to prepare for entering a filter value.</t>
+          <t>Click on the adjustments icon to open the settings menu.</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
+          <t>`page.locator(".pointer.zeb-adjustments").first.click()`</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr"/>
@@ -1418,17 +1314,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>J.6</t>
+          <t>I.3</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Fill the 'Filter Columns Input' textbox with the value '6' to filter columns containing '6'.</t>
+          <t>Click on the 'Save Preference' button to save the current column visibility settings.</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("6")`</t>
+          <t>`page.get_by_text("Save Preference").click()`</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr"/>
@@ -1438,17 +1334,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>J.7</t>
+          <t>I.4</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Press 'Enter' to apply the filter and display the relevant columns.</t>
+          <t>Click on the adjustments icon again to reopen the settings menu.</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").press("Enter")`</t>
+          <t>`page.locator(".pointer.zeb-adjustments").first.click()`</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
@@ -1458,17 +1354,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>K.1</t>
+          <t>I.5</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Check the visibility toggle for the 'Week Gross Units Average Column' to make it visible.</t>
+          <t>Click on the 'Reset Preference' button to reset the column visibility settings to their default state.</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Week Gross Units Average Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_text("Reset Preference").click()`</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
@@ -1476,39 +1372,26 @@
       <c r="F51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>K.2</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Click on the '6 Week Aged Net Units Average' column to select it.</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_label("Column List 9 Columns").get_by_text("6 Week Aged Net Units Average", exact=True).click()`</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr"/>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr"/>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>--- PRODUCT COLUMN CONFIGURATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>K.3</t>
+          <t>J.1</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'LY 6 Week Aged Net Units' column to select it.</t>
+          <t>Click on the horizontal scroll container to ensure the view is scrolled to the appropriate section.</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("LY 6 Week Aged Net Units").get_by_text("LY 6 Week Aged Net Units").click()`</t>
+          <t>`page.locator(".ag-body-horizontal-scroll-container").first.click()`</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
@@ -1518,17 +1401,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>K.4</t>
+          <t>J.2</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Click on the '% Change 6 Week Aged Net' column to select it.</t>
+          <t>Click on the 'Products columns (0) TopBottom' button to open the column selection menu.</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("% Change 6 Week Aged Net").click()`</t>
+          <t>`page.get_by_text("Products columns (0) TopBottom").click()`</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr"/>
@@ -1538,17 +1421,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>K.5</t>
+          <t>J.3</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Filter Columns Input' textbox to clear the filter.</t>
+          <t>Click on the 'Products' section to focus on the product-related columns.</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
+          <t>`page.get_by_text("Products").click()`</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr"/>
@@ -1558,17 +1441,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>K.6</t>
+          <t>J.4</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Clear the 'Filter Columns Input' textbox by filling it with an empty value.</t>
+          <t>Click on the button within the 'Products columns (0)' card to open the column configuration options.</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("")`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Products columns (0)").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
@@ -1578,17 +1461,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>K.7</t>
+          <t>J.5</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Press 'Enter' to reset the filter and display all columns.</t>
+          <t>Click on the 'Filter Columns Input' textbox to prepare for entering a filter value.</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").press("Enter")`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr"/>
@@ -1598,17 +1481,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>M.1</t>
+          <t>J.6</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns.</t>
+          <t>Fill the 'Filter Columns Input' textbox with the value '6' to filter columns containing '6'.</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("6")`</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr"/>
@@ -1618,17 +1501,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>M.2</t>
+          <t>J.7</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible again.</t>
+          <t>Press 'Enter' to apply the filter and display the relevant columns.</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").press("Enter")`</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
@@ -1636,39 +1519,26 @@
       <c r="F59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>N.1</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Click on the first column in the column list to select it.</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("#ag-87 &gt; .ag-column-panel &gt; .ag-column-select &gt; .ag-column-select-list &gt; .ag-virtual-list-viewport &gt; .ag-virtual-list-container &gt; div &gt; .ag-column-select-column").first.click()`</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr"/>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>--- COLUMN FILTERING AND SELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>N.2</t>
+          <t>K.1</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the visibility toggle for the 'System Forecast Base (Plan Week) Column' to hide it.</t>
+          <t>Check the visibility toggle for the 'Week Gross Units Average Column' to make it visible.</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_role("treeitem", name="Week Gross Units Average Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
@@ -1678,17 +1548,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>N.3</t>
+          <t>K.2</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the visibility toggle for the 'System Forecast Promotion (Plan Week) Column' to hide it.</t>
+          <t>Click on the '6 Week Aged Net Units Average' column to select it.</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_label("Column List 9 Columns").get_by_text("6 Week Aged Net Units Average", exact=True).click()`</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
@@ -1698,17 +1568,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>N.4</t>
+          <t>K.3</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the visibility toggle for the 'System Forecast Total (Plan+1)' column to hide it.</t>
+          <t>Click on the 'LY 6 Week Aged Net Units' column to select it.</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan+1").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_label("LY 6 Week Aged Net Units").get_by_text("LY 6 Week Aged Net Units").click()`</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr"/>
@@ -1718,17 +1588,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>N.5</t>
+          <t>K.4</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the visibility toggle for the 'System Forecast Base (Plan+1)' column to hide it.</t>
+          <t>Click on the '% Change 6 Week Aged Net' column to select it.</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan+1").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_text("% Change 6 Week Aged Net").click()`</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr"/>
@@ -1738,17 +1608,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>N.6</t>
+          <t>K.5</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the visibility toggle for the 'System Forecast Promotion (Plan+1 Week) Column' to hide it.</t>
+          <t>Click on the 'Filter Columns Input' textbox to clear the filter.</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (Plan+1 Week) Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr"/>
@@ -1758,17 +1628,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>N.7</t>
+          <t>K.6</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Click on the column selector in the 7th position to interact with its visibility settings.</t>
+          <t>Clear the 'Filter Columns Input' textbox by filling it with an empty value.</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(7) &gt; .ag-column-select-column").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("")`</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr"/>
@@ -1778,17 +1648,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>N.8</t>
+          <t>K.7</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the visibility toggle for the '6 Week Aged Net Units Average Column' to hide it.</t>
+          <t>Press 'Enter' to reset the filter and display all columns.</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="6 Week Aged Net Units Average Column", exact=True).get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").press("Enter")`</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr"/>
@@ -1796,39 +1666,26 @@
       <c r="F67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>N.9</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Uncheck the visibility toggle for the 'LY 6 Week Aged Net Units' column to hide it.</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="LY 6 Week Aged Net Units").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>--- TOGGLE ALL COLUMNS VISIBILITY ---</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>N.10</t>
+          <t>M.1</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Click on the column selector in the 11th position to interact with its visibility settings.</t>
+          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns.</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(11) &gt; .ag-column-select-column").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr"/>
@@ -1838,17 +1695,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>N.11</t>
+          <t>M.2</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the visibility toggle for the '% Change 6 Week Aged Net' column to hide it.</t>
+          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible again.</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="% Change 6 Week Aged Net").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr"/>
@@ -1856,39 +1713,26 @@
       <c r="F70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>N.12</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Uncheck the visibility toggle for the 'LY 6 Week Scan Units Average' column to hide it.</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="LY 6 Week Scan Units Average").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>--- COLUMN SELECTION AND VISIBILITY MANAGEMENT ---</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>N.13</t>
+          <t>N.1</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the visibility toggle for the '% Change 6 Week Scan Units' column to hide it.</t>
+          <t>Click on the first column in the column list to select it.</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="% Change 6 Week Scan Units").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.locator("#ag-87 &gt; .ag-column-panel &gt; .ag-column-select &gt; .ag-column-select-list &gt; .ag-virtual-list-viewport &gt; .ag-virtual-list-container &gt; div &gt; .ag-column-select-column").first.click()`</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr"/>
@@ -1898,17 +1742,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>N.14</t>
+          <t>N.2</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Click on the column selector in the 14th position to interact with its visibility settings.</t>
+          <t>Uncheck the visibility toggle for the 'System Forecast Base (Plan Week) Column' to hide it.</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(14) &gt; .ag-column-select-column").click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr"/>
@@ -1918,17 +1762,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>N.15</t>
+          <t>N.3</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the visibility toggle for the column in the 15th position to hide it.</t>
+          <t>Uncheck the visibility toggle for the 'System Forecast Promotion (Plan Week) Column' to hide it.</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(15) &gt; .ag-column-select-column").uncheck()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr"/>
@@ -1938,17 +1782,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>O.1</t>
+          <t>N.4</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the visibility toggle for the checkbox controlling column visibility to hide all columns.</t>
+          <t>Uncheck the visibility toggle for the 'System Forecast Total (Plan+1)' column to hide it.</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan+1").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr"/>
@@ -1958,17 +1802,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>O.2</t>
+          <t>N.5</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible.</t>
+          <t>Uncheck the visibility toggle for the 'System Forecast Base (Plan+1)' column to hide it.</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan+1").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr"/>
@@ -1978,17 +1822,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>P.1</t>
+          <t>N.6</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Click on the button within the 'Products columns (0)' card to open its settings.</t>
+          <t>Uncheck the visibility toggle for the 'System Forecast Promotion (Plan+1 Week) Column' to hide it.</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Products columns (0)").get_by_role("button").click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Promotion (Plan+1 Week) Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr"/>
@@ -1998,17 +1842,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>P.2</t>
+          <t>N.7</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Click on the export icon to initiate the export process and prepare to capture the download event.</t>
+          <t>Click on the column selector in the 7th position to interact with its visibility settings.</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(2) &gt; #export-iconId &gt; .icon-color-toolbar-active").click()`</t>
+          <t>`page.locator("div:nth-child(7) &gt; .ag-column-select-column").click()`</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr"/>
@@ -2018,17 +1862,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Q.1</t>
+          <t>N.8</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Click on the informational text to acknowledge the export limit message.</t>
+          <t>Uncheck the visibility toggle for the '6 Week Aged Net Units Average Column' to hide it.</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Please note that a maximum of").click()`</t>
+          <t>`page.get_by_role("treeitem", name="6 Week Aged Net Units Average Column", exact=True).get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr"/>
@@ -2038,17 +1882,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Q.2</t>
+          <t>N.9</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Click on the preferences dropdown to open the preferences menu.</t>
+          <t>Uncheck the visibility toggle for the 'LY 6 Week Aged Net Units' column to hide it.</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.get_by_role("treeitem", name="LY 6 Week Aged Net Units").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr"/>
@@ -2058,17 +1902,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Q.3</t>
+          <t>N.10</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Save Preference' to save the current settings.</t>
+          <t>Click on the column selector in the 11th position to interact with its visibility settings.</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Save Preference").click()`</t>
+          <t>`page.locator("div:nth-child(11) &gt; .ag-column-select-column").click()`</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr"/>
@@ -2078,17 +1922,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Q.4</t>
+          <t>N.11</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Click on the preferences dropdown again to reopen the preferences menu.</t>
+          <t>Uncheck the visibility toggle for the '% Change 6 Week Aged Net' column to hide it.</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.get_by_role("treeitem", name="% Change 6 Week Aged Net").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr"/>
@@ -2098,17 +1942,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Q.5</t>
+          <t>N.12</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Reset Preference' to reset the settings to their default state.</t>
+          <t>Uncheck the visibility toggle for the 'LY 6 Week Scan Units Average' column to hide it.</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Reset Preference").click()`</t>
+          <t>`page.get_by_role("treeitem", name="LY 6 Week Scan Units Average").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr"/>
@@ -2118,17 +1962,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>R.1</t>
+          <t>N.13</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Click on the header cell to open the sorting or filtering options for the first column.</t>
+          <t>Uncheck the visibility toggle for the '% Change 6 Week Scan Units' column to hide it.</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-header-cell.ag-column-first.ag-header-parent-hidden.ag-header-cell-sortable &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container").click()`</t>
+          <t>`page.get_by_role("treeitem", name="% Change 6 Week Scan Units").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr"/>
@@ -2138,17 +1982,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>R.2</t>
+          <t>N.14</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Product' text within the grid to select the 'Product' column.</t>
+          <t>Click on the column selector in the 14th position to interact with its visibility settings.</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-row-dimentional-grid").get_by_text("Product").click()`</t>
+          <t>`page.locator("div:nth-child(14) &gt; .ag-column-select-column").click()`</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr"/>
@@ -2158,17 +2002,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>S.1</t>
+          <t>N.15</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Select 'Product 1' from the list of available products by clicking on its name in the grid.</t>
+          <t>Uncheck the visibility toggle for the column in the 15th position to hide it.</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Product 1").click()`</t>
+          <t>`page.locator("div:nth-child(15) &gt; .ag-column-select-column").uncheck()`</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr"/>
@@ -2176,39 +2020,26 @@
       <c r="F86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>S.2</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Click on the filter icon in the header to open the filter options for the column.</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button &gt; .ag-icon").first.click()`</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr"/>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>--- FINAL VISIBILITY TOGGLE ---</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>S.3</t>
+          <t>O.1</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Click on the filter body wrapper to activate the filter input area for further configuration.</t>
+          <t>Uncheck the visibility toggle for the checkbox controlling column visibility to hide all columns.</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-filter-body-wrapper").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr"/>
@@ -2218,17 +2049,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>T.1</t>
+          <t>O.2</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Open the filtering operator dropdown to select a filter condition.</t>
+          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible.</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("combobox", name="Filtering operator").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr"/>
@@ -2236,39 +2067,26 @@
       <c r="F89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>T.2</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>Select the 'Contains' option from the filtering operator dropdown.</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("option", name="Contains").click()`</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr"/>
-      <c r="E90" s="4" t="inlineStr"/>
-      <c r="F90" s="4" t="inlineStr"/>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>--- EXPORT PROCESS ---</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>T.3</t>
+          <t>P.1</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Contains' text to confirm the selection.</t>
+          <t>Click on the button within the 'Products columns (0)' card to open its settings.</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Contains").click()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Products columns (0)").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr"/>
@@ -2278,17 +2096,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>T.4</t>
+          <t>P.2</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Does not contain' text to explore or select this filter condition.</t>
+          <t>Click on the export icon to initiate the export process and prepare to capture the download event.</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Does not contain").click()`</t>
+          <t>`page.locator("div:nth-child(2) &gt; #export-iconId &gt; .icon-color-toolbar-active").click()`</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr"/>
@@ -2296,39 +2114,26 @@
       <c r="F92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>T.5</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>Reopen the filtering operator dropdown to select another filter condition.</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("combobox", name="Filtering operator").click()`</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr"/>
-      <c r="E93" s="4" t="inlineStr"/>
-      <c r="F93" s="4" t="inlineStr"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>--- PREFERENCES MANAGEMENT ---</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>T.6</t>
+          <t>Q.1</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Equals' option from the filtering operator dropdown.</t>
+          <t>Click on the informational text to acknowledge the export limit message.</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Equals").click()`</t>
+          <t>`page.get_by_text("Please note that a maximum of").click()`</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr"/>
@@ -2338,17 +2143,17 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>T.7</t>
+          <t>Q.2</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Equals' text to confirm the selection.</t>
+          <t>Click on the preferences dropdown to open the preferences menu.</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Equals").click()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr"/>
@@ -2358,17 +2163,17 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>T.8</t>
+          <t>Q.3</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Does not equal' text to explore or select this filter condition.</t>
+          <t>Click on 'Save Preference' to save the current settings.</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Does not equal").click()`</t>
+          <t>`page.get_by_text("Save Preference").click()`</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr"/>
@@ -2378,17 +2183,17 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>T.9</t>
+          <t>Q.4</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Does not equal' text again to confirm or toggle the selection.</t>
+          <t>Click on the preferences dropdown again to reopen the preferences menu.</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Does not equal").click()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr"/>
@@ -2398,17 +2203,17 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>T.10</t>
+          <t>Q.5</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Begins with' option from the filtering operator dropdown.</t>
+          <t>Click on 'Reset Preference' to reset the settings to their default state.</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Begins with").click()`</t>
+          <t>`page.get_by_text("Reset Preference").click()`</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr"/>
@@ -2416,39 +2221,26 @@
       <c r="F98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>T.11</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Begins with' text to confirm the selection.</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Begins with").click()`</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr"/>
-      <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr"/>
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>--- GRID INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>T.12</t>
+          <t>R.1</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Ends with' option from the filtering operator dropdown.</t>
+          <t>Click on the header cell to open the sorting or filtering options for the first column.</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Ends with").click()`</t>
+          <t>`page.locator(".ag-header-cell.ag-column-first.ag-header-parent-hidden.ag-header-cell-sortable &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container").click()`</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr"/>
@@ -2458,17 +2250,17 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>T.13</t>
+          <t>R.2</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Ends with' text to confirm the selection.</t>
+          <t>Click on the 'Product' text within the grid to select the 'Product' column.</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Ends with").click()`</t>
+          <t>`page.locator("esp-row-dimentional-grid").get_by_text("Product").click()`</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr"/>
@@ -2476,39 +2268,26 @@
       <c r="F101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>T.14</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>Select the 'Blank' option from the filtering operator dropdown.</t>
-        </is>
-      </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("option", name="Blank", exact=True).click()`</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr"/>
-      <c r="E102" s="4" t="inlineStr"/>
-      <c r="F102" s="4" t="inlineStr"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>--- PRODUCT SELECTION AND FILTER ACTIVATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>U.1</t>
+          <t>S.1</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'AND' text to set the logical operator for combining filter conditions.</t>
+          <t>Select 'Product 1' from the list of available products by clicking on its name in the grid.</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("AND", exact=True).click()`</t>
+          <t>`page.get_by_text("Product 1").click()`</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr"/>
@@ -2518,17 +2297,17 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>U.2</t>
+          <t>S.2</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'OR' text to set the logical operator for combining filter conditions.</t>
+          <t>Click on the filter icon in the header to open the filter options for the column.</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("OR", exact=True).click()`</t>
+          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button &gt; .ag-icon").first.click()`</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr"/>
@@ -2538,17 +2317,17 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>U.3</t>
+          <t>S.3</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Clear' button to remove all applied filters.</t>
+          <t>Click on the filter body wrapper to activate the filter input area for further configuration.</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Clear").click()`</t>
+          <t>`page.locator(".ag-filter-body-wrapper").click()`</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr"/>
@@ -2556,39 +2335,26 @@
       <c r="F105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>U.4</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Reset' button to reset the filter settings to their default state.</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("button", name="Reset").click()`</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr"/>
-      <c r="E106" s="4" t="inlineStr"/>
-      <c r="F106" s="4" t="inlineStr"/>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>--- FILTER OPERATOR SELECTION AND EXPLORATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>U.5</t>
+          <t>T.1</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Click on the filter icon again to close the filter options.</t>
+          <t>Open the filtering operator dropdown to select a filter condition.</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button &gt; .ag-icon").first.click()`</t>
+          <t>`page.get_by_role("combobox", name="Filtering operator").click()`</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr"/>
@@ -2598,17 +2364,17 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>V.1</t>
+          <t>T.2</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to apply the selected filter conditions.</t>
+          <t>Select the 'Contains' option from the filtering operator dropdown.</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Apply").click()`</t>
+          <t>`page.get_by_role("option", name="Contains").click()`</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr"/>
@@ -2618,17 +2384,17 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>V.2</t>
+          <t>T.3</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Click on the first occurrence of the text 'ARNOLD-BRWNBRY-OROWT' within a span element to select the row.</t>
+          <t>Click on the 'Contains' text to confirm the selection.</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span").filter(has_text="ARNOLD-BRWNBRY-OROWT").first.click()`</t>
+          <t>`page.get_by_text("Contains").click()`</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr"/>
@@ -2638,17 +2404,17 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>V.3</t>
+          <t>T.4</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the row containing 'ARNOLD-BRWNBRY-OROWT' to toggle its selection.</t>
+          <t>Click on the 'Does not contain' text to explore or select this filter condition.</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("gridcell", name="Press Space to toggle row selection (unchecked)  ARNOLD-BRWNBRY-OROWT").get_by_label("Press Space to toggle row").check()`</t>
+          <t>`page.get_by_text("Does not contain").click()`</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr"/>
@@ -2658,17 +2424,17 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>W.1</t>
+          <t>T.5</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Right-click on the row containing 'ARNOLD-BRWNBRY-OROWT' to open the context menu.</t>
+          <t>Reopen the filtering operator dropdown to select another filter condition.</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-row-dimentional-grid span").filter(has_text=re.compile(r"^ARNOLD-BRWNBRY-OROWT$")).click(button="right")`</t>
+          <t>`page.get_by_role("combobox", name="Filtering operator").click()`</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr"/>
@@ -2678,17 +2444,17 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>W.2</t>
+          <t>T.6</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Click on the row containing 'ARNOLD-BRWNBRY-OROWT' to select it.</t>
+          <t>Select the 'Equals' option from the filtering operator dropdown.</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-row-dimentional-grid").get_by_text("ARNOLD-BRWNBRY-OROWT").click()`</t>
+          <t>`page.get_by_role("option", name="Equals").click()`</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr"/>
@@ -2698,17 +2464,17 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>W.3</t>
+          <t>T.7</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Click on the row containing 'ARNOLD-BRWNBRY-OROWT' again, possibly to confirm or toggle the selection.</t>
+          <t>Click on the 'Equals' text to confirm the selection.</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-row-dimentional-grid").get_by_text("ARNOLD-BRWNBRY-OROWT").click()`</t>
+          <t>`page.get_by_text("Equals").click()`</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr"/>
@@ -2718,17 +2484,17 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>X.1</t>
+          <t>T.8</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Click on the span element containing the text 'ARTESANO' to select the corresponding row.</t>
+          <t>Click on the 'Does not equal' text to explore or select this filter condition.</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span").filter(has_text=re.compile(r"^ARTESANO$")).click()`</t>
+          <t>`page.get_by_text("Does not equal").click()`</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr"/>
@@ -2738,17 +2504,17 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>X.2</t>
+          <t>T.9</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Click on the text 'ARTESANO' to confirm or highlight the selection.</t>
+          <t>Click on the 'Does not equal' text again to confirm or toggle the selection.</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("ARTESANO").click()`</t>
+          <t>`page.get_by_text("Does not equal").click()`</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr"/>
@@ -2758,17 +2524,17 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>Y.1</t>
+          <t>T.10</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the row containing 'ARTESANO' to toggle its selection.</t>
+          <t>Select the 'Begins with' option from the filtering operator dropdown.</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("gridcell", name="Press Space to toggle row selection (unchecked)  ARTESANO").get_by_label("Press Space to toggle row").check()`</t>
+          <t>`page.get_by_role("option", name="Begins with").click()`</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr"/>
@@ -2778,17 +2544,17 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Y.2</t>
+          <t>T.11</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Double-click on the checkbox within the row to perform an additional action, possibly to confirm selection.</t>
+          <t>Click on the 'Begins with' text to confirm the selection.</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-cell-value.ag-cell.ag-cell-not-inline-editing.ag-cell-normal-height.ag-cell-last-left-pinned.ag-column-first.no-border.ag-cell-focus &gt; .ag-cell-wrapper &gt; .ag-group-checkbox").dblclick()`</t>
+          <t>`page.get_by_text("Begins with").click()`</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr"/>
@@ -2798,17 +2564,17 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Z.1</t>
+          <t>T.12</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Click on the text 'System Forecast Total (Plan' to interact with the column header or data.</t>
+          <t>Select the 'Ends with' option from the filtering operator dropdown.</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("System Forecast Total (Plan").nth(3).click()`</t>
+          <t>`page.get_by_role("option", name="Ends with").click()`</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr"/>
@@ -2818,17 +2584,17 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Z.2</t>
+          <t>T.13</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Click on the descending sort icon in the column header to sort the data in descending order.</t>
+          <t>Click on the 'Ends with' text to confirm the selection.</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-cell-label-container.ag-header-cell-sorted-desc &gt; .ag-header-cell-label &gt; .ag-sort-indicator-container &gt; .ag-sort-indicator-icon.ag-sort-descending-icon &gt; .ag-icon").click()`</t>
+          <t>`page.get_by_text("Ends with").click()`</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr"/>
@@ -2838,17 +2604,17 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>Z.3</t>
+          <t>T.14</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Click on the ascending sort icon in the column header to sort the data in ascending order.</t>
+          <t>Select the 'Blank' option from the filtering operator dropdown.</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-cell-label-container.ag-header-cell-sorted-asc &gt; .ag-header-cell-label &gt; .ag-sort-indicator-container &gt; .ag-sort-indicator-icon.ag-sort-ascending-icon &gt; .ag-icon").click()`</t>
+          <t>`page.get_by_role("option", name="Blank", exact=True).click()`</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr"/>
@@ -2856,39 +2622,26 @@
       <c r="F120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>Z.4</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>Click on the header icon to interact with the column, possibly to open a menu or perform an action.</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".ag-header-cell.ag-header-parent-hidden.ag-header-cell-sortable.ag-header-background.ag-focus-managed.ag-header-active &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container &gt; .ag-header-icon &gt; .ag-icon").click()`</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr"/>
-      <c r="E121" s="4" t="inlineStr"/>
-      <c r="F121" s="4" t="inlineStr"/>
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>--- LOGICAL OPERATOR AND FILTER RESET ---</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>[.1</t>
+          <t>U.1</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Click on the filter body wrapper to open the filter options.</t>
+          <t>Click on the 'AND' text to set the logical operator for combining filter conditions.</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-filter-body-wrapper").click()`</t>
+          <t>`page.get_by_text("AND", exact=True).click()`</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr"/>
@@ -2898,17 +2651,17 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>[.2</t>
+          <t>U.2</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Click on the combobox labeled 'Filtering operator' to open the dropdown menu.</t>
+          <t>Click on the 'OR' text to set the logical operator for combining filter conditions.</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("combobox", name="Filtering operator").click()`</t>
+          <t>`page.get_by_text("OR", exact=True).click()`</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr"/>
@@ -2918,17 +2671,17 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>[.3</t>
+          <t>U.3</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Equals' option from the dropdown menu.</t>
+          <t>Click on the 'Clear' button to remove all applied filters.</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Equals").click()`</t>
+          <t>`page.get_by_role("button", name="Clear").click()`</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr"/>
@@ -2938,17 +2691,17 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>[.4</t>
+          <t>U.4</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Click on the text 'Equals' to confirm the selection.</t>
+          <t>Click on the 'Reset' button to reset the filter settings to their default state.</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Equals").click()`</t>
+          <t>`page.get_by_role("button", name="Reset").click()`</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr"/>
@@ -2958,17 +2711,17 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>[.5</t>
+          <t>U.5</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Does not equal' option from the dropdown menu.</t>
+          <t>Click on the filter icon again to close the filter options.</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Does not equal").click()`</t>
+          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button &gt; .ag-icon").first.click()`</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr"/>
@@ -2976,39 +2729,26 @@
       <c r="F126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>[.6</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>Click on the text 'Does not equal' to confirm the selection.</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Does not equal").click()`</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr"/>
-      <c r="E127" s="4" t="inlineStr"/>
-      <c r="F127" s="4" t="inlineStr"/>
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>--- FILTER APPLICATION AND ROW SELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>[.7</t>
+          <t>V.1</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Greater than' option from the dropdown menu.</t>
+          <t>Click on the 'Apply' button to apply the selected filter conditions.</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Greater than", exact=True).click()`</t>
+          <t>`page.get_by_role("button", name="Apply").click()`</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr"/>
@@ -3018,17 +2758,17 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>[.8</t>
+          <t>V.2</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Click on the text 'Greater than' to confirm the selection.</t>
+          <t>Click on the first occurrence of the text 'ARNOLD-BRWNBRY-OROWT' within a span element to select the row.</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Greater than").click()`</t>
+          <t>`page.locator("span").filter(has_text="ARNOLD-BRWNBRY-OROWT").first.click()`</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr"/>
@@ -3038,17 +2778,17 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>[.9</t>
+          <t>V.3</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Click on the text 'Greater than or equal to' to confirm the selection.</t>
+          <t>Check the checkbox for the row containing 'ARNOLD-BRWNBRY-OROWT' to toggle its selection.</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Greater than or equal to").click()`</t>
+          <t>`page.get_by_role("gridcell", name="Press Space to toggle row selection (unchecked)  ARNOLD-BRWNBRY-OROWT").get_by_label("Press Space to toggle row").check()`</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr"/>
@@ -3056,39 +2796,26 @@
       <c r="F130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>[.10</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>Click on the text 'Greater than or equal to' again, possibly to confirm or toggle the selection.</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Greater than or equal to").click()`</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr"/>
-      <c r="E131" s="4" t="inlineStr"/>
-      <c r="F131" s="4" t="inlineStr"/>
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>--- ROW CONTEXT MENU AND SELECTION CONFIRMATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>[.11</t>
+          <t>W.1</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Less than' option from the dropdown menu.</t>
+          <t>Right-click on the row containing 'ARNOLD-BRWNBRY-OROWT' to open the context menu.</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Less than", exact=True).click()`</t>
+          <t>`page.locator("esp-row-dimentional-grid span").filter(has_text=re.compile(r"^ARNOLD-BRWNBRY-OROWT$")).click(button="right")`</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr"/>
@@ -3098,17 +2825,17 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>[.12</t>
+          <t>W.2</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Click on the text 'Less than' to confirm the selection.</t>
+          <t>Click on the row containing 'ARNOLD-BRWNBRY-OROWT' to select it.</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Less than").click()`</t>
+          <t>`page.locator("esp-row-dimentional-grid").get_by_text("ARNOLD-BRWNBRY-OROWT").click()`</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr"/>
@@ -3118,17 +2845,17 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>[.13</t>
+          <t>W.3</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Between' option from the dropdown menu.</t>
+          <t>Click on the row containing 'ARNOLD-BRWNBRY-OROWT' again, possibly to confirm or toggle the selection.</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Between").click()`</t>
+          <t>`page.locator("esp-row-dimentional-grid").get_by_text("ARNOLD-BRWNBRY-OROWT").click()`</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr"/>
@@ -3136,39 +2863,26 @@
       <c r="F134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>[.14</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>Click on the text 'Between' to confirm the selection.</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Between").click()`</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr"/>
-      <c r="E135" s="4" t="inlineStr"/>
-      <c r="F135" s="4" t="inlineStr"/>
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>--- ADDITIONAL ROW SELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>[.15</t>
+          <t>X.1</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Blank' option from the dropdown menu.</t>
+          <t>Click on the span element containing the text 'ARTESANO' to select the corresponding row.</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Blank", exact=True).click()`</t>
+          <t>`page.locator("span").filter(has_text=re.compile(r"^ARTESANO$")).click()`</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr"/>
@@ -3178,17 +2892,17 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>[.16</t>
+          <t>X.2</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Click on the text 'AND' to set the logical operator for the filter.</t>
+          <t>Click on the text 'ARTESANO' to confirm or highlight the selection.</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("AND", exact=True).click()`</t>
+          <t>`page.get_by_text("ARTESANO").click()`</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr"/>
@@ -3196,39 +2910,26 @@
       <c r="F137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>[.17</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t>Click on the text 'OR' to set the logical operator for the filter.</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("OR", exact=True).click()`</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="inlineStr"/>
-      <c r="E138" s="4" t="inlineStr"/>
-      <c r="F138" s="4" t="inlineStr"/>
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>--- ROW SELECTION AND INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>[.1</t>
+          <t>Y.1</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Click on the spinbutton labeled 'Filter Value' to activate the input field.</t>
+          <t>Check the checkbox for the row containing 'ARTESANO' to toggle its selection.</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("spinbutton", name="Filter Value").click()`</t>
+          <t>`page.get_by_role("gridcell", name="Press Space to toggle row selection (unchecked)  ARTESANO").get_by_label("Press Space to toggle row").check()`</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr"/>
@@ -3238,17 +2939,17 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>[.2</t>
+          <t>Y.2</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Fill the spinbutton labeled 'Filter Value' with the value '1'.</t>
+          <t>Double-click on the checkbox within the row to perform an additional action, possibly to confirm selection.</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("spinbutton", name="Filter Value").fill("1")`</t>
+          <t>`page.locator(".ag-cell-value.ag-cell.ag-cell-not-inline-editing.ag-cell-normal-height.ag-cell-last-left-pinned.ag-column-first.no-border.ag-cell-focus &gt; .ag-cell-wrapper &gt; .ag-group-checkbox").dblclick()`</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr"/>
@@ -3256,39 +2957,26 @@
       <c r="F140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>[.3</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>Click on the spinbutton labeled 'Filter Value' again, possibly to confirm the input.</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("spinbutton", name="Filter Value").click()`</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr"/>
-      <c r="E141" s="4" t="inlineStr"/>
-      <c r="F141" s="4" t="inlineStr"/>
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>--- COLUMN HEADER INTERACTION AND SORTING ---</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>[.4</t>
+          <t>Z.1</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to apply the filter settings.</t>
+          <t>Click on the text 'System Forecast Total (Plan' to interact with the column header or data.</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Apply").click()`</t>
+          <t>`page.get_by_text("System Forecast Total (Plan").nth(3).click()`</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr"/>
@@ -3298,17 +2986,17 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>].1</t>
+          <t>Z.2</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Click on the header cell to interact with the column, possibly to open a menu or perform an action.</t>
+          <t>Click on the descending sort icon in the column header to sort the data in descending order.</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-header-cell.ag-header-parent-hidden.ag-header-cell-sortable.ag-header-background.ag-focus-managed.ag-header-cell-filtered &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container").click()`</t>
+          <t>`page.locator(".ag-cell-label-container.ag-header-cell-sorted-desc &gt; .ag-header-cell-label &gt; .ag-sort-indicator-container &gt; .ag-sort-indicator-icon.ag-sort-descending-icon &gt; .ag-icon").click()`</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr"/>
@@ -3318,17 +3006,17 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>].2</t>
+          <t>Z.3</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Click on the filter button in the column header to activate the filter options.</t>
+          <t>Click on the ascending sort icon in the column header to sort the data in ascending order.</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button.ag-filter-active &gt; .ag-icon").click()`</t>
+          <t>`page.locator(".ag-cell-label-container.ag-header-cell-sorted-asc &gt; .ag-header-cell-label &gt; .ag-sort-indicator-container &gt; .ag-sort-indicator-icon.ag-sort-ascending-icon &gt; .ag-icon").click()`</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr"/>
@@ -3338,17 +3026,17 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>].3</t>
+          <t>Z.4</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Clear' button to remove any existing filters.</t>
+          <t>Click on the header icon to interact with the column, possibly to open a menu or perform an action.</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Clear").click()`</t>
+          <t>`page.locator(".ag-header-cell.ag-header-parent-hidden.ag-header-cell-sortable.ag-header-background.ag-focus-managed.ag-header-active &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container &gt; .ag-header-icon &gt; .ag-icon").click()`</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr"/>
@@ -3356,39 +3044,26 @@
       <c r="F145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>^.1</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Reset' button to reset the filter settings to their default state.</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("button", name="Reset").click()`</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr"/>
-      <c r="E146" s="4" t="inlineStr"/>
-      <c r="F146" s="4" t="inlineStr"/>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>--- FILTER OPTIONS INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>^.2</t>
+          <t>[.1</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Click on the button within the 'Products columns (0)' card to open the column visibility configuration.</t>
+          <t>Click on the filter body wrapper to open the filter options.</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Products columns (0)").get_by_role("button").click()`</t>
+          <t>`page.locator(".ag-filter-body-wrapper").click()`</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr"/>
@@ -3398,17 +3073,17 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>^.3</t>
+          <t>[.2</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Filter Columns Input' textbox to activate it for entering a search term.</t>
+          <t>Click on the combobox labeled 'Filtering operator' to open the dropdown menu.</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
+          <t>`page.get_by_role("combobox", name="Filtering operator").click()`</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr"/>
@@ -3418,17 +3093,17 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>^.4</t>
+          <t>[.3</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns.</t>
+          <t>Select the 'Equals' option from the dropdown menu.</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
+          <t>`page.get_by_role("option", name="Equals").click()`</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr"/>
@@ -3438,17 +3113,17 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>^.5</t>
+          <t>[.4</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible.</t>
+          <t>Click on the text 'Equals' to confirm the selection.</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+          <t>`page.get_by_text("Equals").click()`</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr"/>
@@ -3458,17 +3133,17 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>^.6</t>
+          <t>[.5</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the checkbox for the 'System Forecast Total (Plan Week) Column' to hide this specific column.</t>
+          <t>Select the 'Does not equal' option from the dropdown menu.</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_role("option", name="Does not equal").click()`</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr"/>
@@ -3478,17 +3153,17 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>^.7</t>
+          <t>[.6</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the checkbox for the 'System Forecast Base (Plan Week) Column' to hide this specific column.</t>
+          <t>Click on the text 'Does not equal' to confirm the selection.</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_text("Does not equal").click()`</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr"/>
@@ -3498,17 +3173,17 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>^.8</t>
+          <t>[.7</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Click on the label for the 'System Forecast Promotion (Plan Week) Column' to interact with or highlight it.</t>
+          <t>Select the 'Greater than' option from the dropdown menu.</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("System Forecast Promotion (Plan Week) Column").get_by_text("System Forecast Promotion (").click()`</t>
+          <t>`page.get_by_role("option", name="Greater than", exact=True).click()`</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr"/>
@@ -3518,17 +3193,17 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>^.9</t>
+          <t>[.8</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Click on the label for the 'System Forecast Total (Plan+1)' column to interact with or highlight it.</t>
+          <t>Click on the text 'Greater than' to confirm the selection.</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("System Forecast Total (Plan+1").get_by_text("System Forecast Total (Plan+1").click()`</t>
+          <t>`page.get_by_text("Greater than").click()`</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr"/>
@@ -3538,17 +3213,17 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>^.10</t>
+          <t>[.9</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Click on the label for the 'System Forecast Base (Plan+1)' column to interact with or highlight it.</t>
+          <t>Click on the text 'Greater than or equal to' to confirm the selection.</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("System Forecast Base (Plan+1").get_by_text("System Forecast Base (Plan+1").click()`</t>
+          <t>`page.get_by_text("Greater than or equal to").click()`</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr"/>
@@ -3558,17 +3233,17 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>^.11</t>
+          <t>[.10</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Click on the label for the 'System Forecast Promotion (Plan+1 Week) Column' to interact with or highlight it.</t>
+          <t>Click on the text 'Greater than or equal to' again, possibly to confirm or toggle the selection.</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("System Forecast Promotion (Plan+1 Week) Column").get_by_text("System Forecast Promotion (").click()`</t>
+          <t>`page.get_by_text("Greater than or equal to").click()`</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr"/>
@@ -3578,17 +3253,17 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>_.1</t>
+          <t>[.11</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Click on the label for the '6 Week Gross Units Average' column to interact with or highlight it.</t>
+          <t>Select the 'Less than' option from the dropdown menu.</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("6 Week Gross Units Average").get_by_text("Week Gross Units Average").click()`</t>
+          <t>`page.get_by_role("option", name="Less than", exact=True).click()`</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr"/>
@@ -3598,17 +3273,17 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>_.2</t>
+          <t>[.12</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Click on the label for the 'LY 6 Week Aged Net Units' column to interact with or highlight it.</t>
+          <t>Click on the text 'Less than' to confirm the selection.</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("LY 6 Week Aged Net Units").get_by_text("LY 6 Week Aged Net Units").click()`</t>
+          <t>`page.get_by_text("Less than").click()`</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr"/>
@@ -3618,17 +3293,17 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>_.3</t>
+          <t>[.13</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Click on the label for the '6 Week Aged Net Units Average Column' to interact with or highlight it.</t>
+          <t>Select the 'Between' option from the dropdown menu.</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("6 Week Aged Net Units Average Column", exact=True).get_by_text("Week Aged Net Units Average").click()`</t>
+          <t>`page.get_by_role("option", name="Between").click()`</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr"/>
@@ -3638,17 +3313,17 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>_.4</t>
+          <t>[.14</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Click on the label for the '6 Week Aged Net Units Average Column' again, possibly to confirm or toggle the selection.</t>
+          <t>Click on the text 'Between' to confirm the selection.</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("6 Week Aged Net Units Average Column", exact=True).get_by_text("Week Aged Net Units Average").click()`</t>
+          <t>`page.get_by_text("Between").click()`</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr"/>
@@ -3658,17 +3333,17 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>_.5</t>
+          <t>[.15</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Click on the label for the '% Change 6 Week Aged Net' column to interact with or highlight it.</t>
+          <t>Select the 'Blank' option from the dropdown menu.</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("% Change 6 Week Aged Net").get_by_text("% Change 6 Week Aged Net").click()`</t>
+          <t>`page.get_by_role("option", name="Blank", exact=True).click()`</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr"/>
@@ -3678,17 +3353,17 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>_.6</t>
+          <t>[.16</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Click on the label for the '% Change 6 Week Scan Units' column to interact with or highlight it.</t>
+          <t>Click on the text 'AND' to set the logical operator for the filter.</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("% Change 6 Week Scan Units").get_by_text("% Change 6 Week Scan Units").click()`</t>
+          <t>`page.get_by_text("AND", exact=True).click()`</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr"/>
@@ -3698,17 +3373,17 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>_.7</t>
+          <t>[.17</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Click on the label for the '6 Week Aged Returns Units' column to interact with or highlight it.</t>
+          <t>Click on the text 'OR' to set the logical operator for the filter.</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("6 Week Aged Returns Units").get_by_text("6 Week Aged Returns Units").click()`</t>
+          <t>`page.get_by_text("OR", exact=True).click()`</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr"/>
@@ -3716,39 +3391,26 @@
       <c r="F163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>_.8</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>Click on the label for the 'Freshness (6 Week Average)' column to interact with or highlight it.</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_label("Freshness (6 Week Average)").get_by_text("Freshness (6 Week Average)").click()`</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr"/>
-      <c r="E164" s="4" t="inlineStr"/>
-      <c r="F164" s="4" t="inlineStr"/>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>--- FILTER VALUE INPUT AND APPLICATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>_.9</t>
+          <t>[.1</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Click on the label for the 'LY 6 Week Scan Units Average' column to interact with or highlight it.</t>
+          <t>Click on the spinbutton labeled 'Filter Value' to activate the input field.</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("LY 6 Week Scan Units Average").get_by_text("LY 6 Week Scan Units Average").click()`</t>
+          <t>`page.get_by_role("spinbutton", name="Filter Value").click()`</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr"/>
@@ -3758,17 +3420,17 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>_.10</t>
+          <t>[.2</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Click on the label for the '6 Week Scan Units Average Column' to interact with or highlight it.</t>
+          <t>Fill the spinbutton labeled 'Filter Value' with the value '1'.</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("6 Week Scan Units Average Column", exact=True).get_by_text("Week Scan Units Average").click()`</t>
+          <t>`page.get_by_role("spinbutton", name="Filter Value").fill("1")`</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr"/>
@@ -3778,17 +3440,17 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>_.11</t>
+          <t>[.3</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Click on the button within the 'Products columns (0)' card again, possibly to close the column visibility configuration.</t>
+          <t>Click on the spinbutton labeled 'Filter Value' again, possibly to confirm the input.</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Products columns (0)").get_by_role("button").click()`</t>
+          <t>`page.get_by_role("spinbutton", name="Filter Value").click()`</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr"/>
@@ -3798,17 +3460,17 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>`.1`</t>
+          <t>[.4</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Set up an expectation for a file download to occur during the subsequent action.</t>
+          <t>Click on the 'Apply' button to apply the filter settings.</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>`with page.expect_download() as download2_info:`</t>
+          <t>`page.get_by_role("button", name="Apply").click()`</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr"/>
@@ -3816,39 +3478,26 @@
       <c r="F168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>`.2`</t>
-        </is>
-      </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>Click on the export icon to initiate the export process. Locate the export icon within the toolbar and click it to start the export.</t>
-        </is>
-      </c>
-      <c r="C169" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("div:nth-child(2) &gt; #export-iconId &gt; .icon-color-toolbar-active").click()`</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr"/>
-      <c r="E169" s="4" t="inlineStr"/>
-      <c r="F169" s="4" t="inlineStr"/>
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>--- FILTER CLEARING AND FINAL INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>`.3`</t>
+          <t>].1</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Capture the downloaded file information after the export action is triggered.</t>
+          <t>Click on the header cell to interact with the column, possibly to open a menu or perform an action.</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>`download2 = download2_info.value`</t>
+          <t>`page.locator(".ag-header-cell.ag-header-parent-hidden.ag-header-cell-sortable.ag-header-background.ag-focus-managed.ag-header-cell-filtered &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container").click()`</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr"/>
@@ -3858,17 +3507,17 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>a.1</t>
+          <t>].2</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Click on the informational message that notifies the user about the export limit. Look for the message text and click to acknowledge it.</t>
+          <t>Click on the filter button in the column header to activate the filter options.</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Please note that a maximum of").click()`</t>
+          <t>`page.locator(".ag-header-icon.ag-header-cell-filter-button.ag-filter-active &gt; .ag-icon").click()`</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr"/>
@@ -3878,17 +3527,17 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>a.2</t>
+          <t>].3</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Open the preference dropdown menu to view the available options for managing preferences. Locate the dropdown menu icon and click it.</t>
+          <t>Click on the 'Clear' button to remove any existing filters.</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.get_by_role("button", name="Clear").click()`</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr"/>
@@ -3896,39 +3545,26 @@
       <c r="F172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="3" t="inlineStr">
-        <is>
-          <t>a.3</t>
-        </is>
-      </c>
-      <c r="B173" s="4" t="inlineStr">
-        <is>
-          <t>Save the current settings by selecting the 'Save Preference' option from the dropdown menu.</t>
-        </is>
-      </c>
-      <c r="C173" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Save Preference").click()`</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr"/>
-      <c r="E173" s="4" t="inlineStr"/>
-      <c r="F173" s="4" t="inlineStr"/>
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>--- RESET AND CONFIGURE COLUMN VISIBILITY PART 1 ---</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>a.4</t>
+          <t>^.1</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Reopen the preference dropdown menu to access the options again. Locate the dropdown menu icon and click it.</t>
+          <t>Click on the 'Reset' button to reset the filter settings to their default state.</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.get_by_role("button", name="Reset").click()`</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr"/>
@@ -3938,17 +3574,17 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>a.5</t>
+          <t>^.2</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Reset the settings to their default state by selecting the 'Reset Preference' option from the dropdown menu.</t>
+          <t>Click on the button within the 'Products columns (0)' card to open the column visibility configuration.</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Reset Preference").click()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Products columns (0)").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr"/>
@@ -3958,17 +3594,17 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>b.1</t>
+          <t>^.3</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Click on the text 'Showing 10 out of 28 123Rows' to interact with the pagination display.</t>
+          <t>Click on the 'Filter Columns Input' textbox to activate it for entering a search term.</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Showing 10 out of 28 123Rows").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr"/>
@@ -3978,17 +3614,17 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>b.2</t>
+          <t>^.4</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Rows per page View 10 row(s)' dropdown to open the options for changing the number of rows displayed.</t>
+          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns.</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Rows per page View 10 row(s)").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr"/>
@@ -3998,17 +3634,17 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>b.3</t>
+          <t>^.5</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Click on the option 'View 10 row(s)' to confirm the selection of 10 rows per page.</t>
+          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible.</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span").filter(has_text=re.compile(r"^View 10 row\(s\)$")).click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr"/>
@@ -4018,17 +3654,17 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>b.4</t>
+          <t>^.6</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Click on the text 'Showing 10 out of' to refresh or interact with the pagination display.</t>
+          <t>Uncheck the checkbox for the 'System Forecast Total (Plan Week) Column' to hide this specific column.</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Showing 10 out of").click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Total (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr"/>
@@ -4038,17 +3674,17 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>b.5</t>
+          <t>^.7</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Click on the first instance of 'View 10 row(s)' to ensure the selection of 10 rows per page.</t>
+          <t>Uncheck the checkbox for the 'System Forecast Base (Plan Week) Column' to hide this specific column.</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("View 10 row(s)").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="System Forecast Base (Plan Week) Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr"/>
@@ -4058,17 +3694,17 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>b.6</t>
+          <t>^.8</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Click on the first instance of 'View 20 row(s)' to change the number of rows displayed to 20.</t>
+          <t>Click on the label for the 'System Forecast Promotion (Plan Week) Column' to interact with or highlight it.</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^View 20 row\(s\)$")).first.click()`</t>
+          <t>`page.get_by_label("System Forecast Promotion (Plan Week) Column").get_by_text("System Forecast Promotion (").click()`</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr"/>
@@ -4078,17 +3714,17 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>b.7</t>
+          <t>^.9</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Click on the text 'Showing 20 out of' to interact with the updated pagination display.</t>
+          <t>Click on the label for the 'System Forecast Total (Plan+1)' column to interact with or highlight it.</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Showing 20 out of").click()`</t>
+          <t>`page.get_by_label("System Forecast Total (Plan+1").get_by_text("System Forecast Total (Plan+1").click()`</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr"/>
@@ -4098,17 +3734,17 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>b.8</t>
+          <t>^.10</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Click on the exact text '12' to navigate to page 12 in the pagination.</t>
+          <t>Click on the label for the 'System Forecast Base (Plan+1)' column to interact with or highlight it.</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("12", exact=True).click()`</t>
+          <t>`page.get_by_label("System Forecast Base (Plan+1").get_by_text("System Forecast Base (Plan+1").click()`</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr"/>
@@ -4118,17 +3754,17 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>b.9</t>
+          <t>^.11</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Click on the link with the text '2' to navigate to page 2 in the pagination.</t>
+          <t>Click on the label for the 'System Forecast Promotion (Plan+1 Week) Column' to interact with or highlight it.</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("a").filter(has_text="2").click()`</t>
+          <t>`page.get_by_label("System Forecast Promotion (Plan+1 Week) Column").get_by_text("System Forecast Promotion (").click()`</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr"/>
@@ -4136,39 +3772,26 @@
       <c r="F184" s="4" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>b.10</t>
-        </is>
-      </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>Click on the left chevron icon to navigate to the previous page in the pagination.</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".zeb-chevron-left").click()`</t>
-        </is>
-      </c>
-      <c r="D185" s="3" t="inlineStr"/>
-      <c r="E185" s="4" t="inlineStr"/>
-      <c r="F185" s="4" t="inlineStr"/>
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>--- RESET AND CONFIGURE COLUMN VISIBILITY PART 2 ---</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>b.11</t>
+          <t>_.1</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Click on the exact text '12' again to navigate back to page 12.</t>
+          <t>Click on the label for the '6 Week Gross Units Average' column to interact with or highlight it.</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("12", exact=True).click()`</t>
+          <t>`page.get_by_label("6 Week Gross Units Average").get_by_text("Week Gross Units Average").click()`</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr"/>
@@ -4178,17 +3801,17 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>b.12</t>
+          <t>_.2</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Click on the exact text '12' once more to confirm navigation to page 12.</t>
+          <t>Click on the label for the 'LY 6 Week Aged Net Units' column to interact with or highlight it.</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("12", exact=True).click()`</t>
+          <t>`page.get_by_label("LY 6 Week Aged Net Units").get_by_text("LY 6 Week Aged Net Units").click()`</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr"/>
@@ -4198,17 +3821,17 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>b.13</t>
+          <t>_.3</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'pagination-last' button to navigate to the last page in the pagination.</t>
+          <t>Click on the label for the '6 Week Aged Net Units Average Column' to interact with or highlight it.</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".pagination-last").click()`</t>
+          <t>`page.get_by_label("6 Week Aged Net Units Average Column", exact=True).get_by_text("Week Aged Net Units Average").click()`</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr"/>
@@ -4218,17 +3841,17 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>b.14</t>
+          <t>_.4</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'zeb-nav-to-first' button to navigate back to the first page in the pagination.</t>
+          <t>Click on the label for the '6 Week Aged Net Units Average Column' again, possibly to confirm or toggle the selection.</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".zeb-nav-to-first").click()`</t>
+          <t>`page.get_by_label("6 Week Aged Net Units Average Column", exact=True).get_by_text("Week Aged Net Units Average").click()`</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr"/>
@@ -4238,17 +3861,17 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>c.1</t>
+          <t>_.5</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox in the row labeled 'Press Space to toggle row selection (unchecked)' to select the row for 'THOMAS BRANDS'.</t>
+          <t>Click on the label for the '% Change 6 Week Aged Net' column to interact with or highlight it.</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("row", name="Press Space to toggle row selection (unchecked)  THOMAS BRANDS").get_by_label("Press Space to toggle row").check()`</t>
+          <t>`page.get_by_label("% Change 6 Week Aged Net").get_by_text("% Change 6 Week Aged Net").click()`</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr"/>
@@ -4258,17 +3881,17 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>c.2</t>
+          <t>_.6</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Click on the card content area to interact with the main filter and summary section.</t>
+          <t>Click on the label for the '% Change 6 Week Scan Units' column to interact with or highlight it.</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".card-content.p-24").click()`</t>
+          <t>`page.get_by_label("% Change 6 Week Scan Units").get_by_text("% Change 6 Week Scan Units").click()`</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr"/>
@@ -4278,17 +3901,17 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>d.1</t>
+          <t>_.7</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Click on the text 'FilterTime Latest Order &amp;' to open the filter options.</t>
+          <t>Click on the label for the '6 Week Aged Returns Units' column to interact with or highlight it.</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("FilterTime Latest Order &amp;").click()`</t>
+          <t>`page.get_by_label("6 Week Aged Returns Units").get_by_text("6 Week Aged Returns Units").click()`</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr"/>
@@ -4298,17 +3921,17 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>d.2</t>
+          <t>_.8</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Filter' button to apply or modify the filter settings.</t>
+          <t>Click on the label for the 'Freshness (6 Week Average)' column to interact with or highlight it.</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Filter$")).click()`</t>
+          <t>`page.get_by_label("Freshness (6 Week Average)").get_by_text("Freshness (6 Week Average)").click()`</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr"/>
@@ -4318,17 +3941,17 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>d.3</t>
+          <t>_.9</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Time' option to select the time-based filter.</t>
+          <t>Click on the label for the 'LY 6 Week Scan Units Average' column to interact with or highlight it.</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Time").click()`</t>
+          <t>`page.get_by_label("LY 6 Week Scan Units Average").get_by_text("LY 6 Week Scan Units Average").click()`</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr"/>
@@ -4338,17 +3961,17 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>d.4</t>
+          <t>_.10</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Latest Order &amp; Plan Week' to apply this specific filter.</t>
+          <t>Click on the label for the '6 Week Scan Units Average Column' to interact with or highlight it.</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Latest Order &amp; Plan Week").first.click()`</t>
+          <t>`page.get_by_label("6 Week Scan Units Average Column", exact=True).get_by_text("Week Scan Units Average").click()`</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr"/>
@@ -4358,17 +3981,17 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>d.5</t>
+          <t>_.11</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Daily Summary Product:THOMAS' to view the daily summary for the product 'THOMAS'.</t>
+          <t>Click on the button within the 'Products columns (0)' card again, possibly to close the column visibility configuration.</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Daily Summary Product:THOMAS").click()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Products columns (0)").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr"/>
@@ -4376,39 +3999,26 @@
       <c r="F196" s="4" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="3" t="inlineStr">
-        <is>
-          <t>d.6</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>Click on 'Daily Summary' to interact with the summary section.</t>
-        </is>
-      </c>
-      <c r="C197" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Daily Summary").click()`</t>
-        </is>
-      </c>
-      <c r="D197" s="3" t="inlineStr"/>
-      <c r="E197" s="4" t="inlineStr"/>
-      <c r="F197" s="4" t="inlineStr"/>
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>--- EXPORT DATA ---</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>d.7</t>
+          <t>`.1`</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Product:THOMAS BRANDS' to focus on the product-specific summary.</t>
+          <t>Set up an expectation for a file download to occur during the subsequent action.</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Product:THOMAS BRANDS").first.click()`</t>
+          <t>`with page.expect_download() as download2_info:`</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr"/>
@@ -4418,17 +4028,17 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>d.8</t>
+          <t>`.2`</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Click on the third instance of the exact text 'Product' to refine the selection.</t>
+          <t>Click on the export icon to initiate the export process. Locate the export icon within the toolbar and click it to start the export.</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Product", exact=True).nth(2).click()`</t>
+          <t>`page.locator("div:nth-child(2) &gt; #export-iconId &gt; .icon-color-toolbar-active").click()`</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr"/>
@@ -4438,17 +4048,17 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>d.9</t>
+          <t>`.3`</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>Click on the second instance of 'THOMAS BRANDS' to confirm the selection of this product.</t>
+          <t>Capture the downloaded file information after the export action is triggered.</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("THOMAS BRANDS").nth(1).click()`</t>
+          <t>`download2 = download2_info.value`</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr"/>
@@ -4456,39 +4066,26 @@
       <c r="F200" s="4" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>d.10</t>
-        </is>
-      </c>
-      <c r="B201" s="4" t="inlineStr">
-        <is>
-          <t>Click on 'Daily Summary Product:THOMAS' again to refresh or interact with the summary.</t>
-        </is>
-      </c>
-      <c r="C201" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Daily Summary Product:THOMAS").click()`</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="inlineStr"/>
-      <c r="E201" s="4" t="inlineStr"/>
-      <c r="F201" s="4" t="inlineStr"/>
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>--- MANAGE PREFERENCES ---</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>e.1</t>
+          <t>a.1</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown to open the multiselect options for filtering.</t>
+          <t>Click on the informational message that notifies the user about the export limit. Look for the message text and click to acknowledge it.</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100").click()`</t>
+          <t>`page.get_by_text("Please note that a maximum of").click()`</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr"/>
@@ -4498,17 +4095,17 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>e.2</t>
+          <t>a.2</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Select the first option in the dropdown list.</t>
+          <t>Open the preference dropdown menu to view the available options for managing preferences. Locate the dropdown menu icon and click it.</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option").first.click()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr"/>
@@ -4518,17 +4115,17 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>e.3</t>
+          <t>a.3</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Select the first option in the dropdown list again, possibly to toggle or confirm the selection.</t>
+          <t>Save the current settings by selecting the 'Save Preference' option from the dropdown menu.</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option").first.click()`</t>
+          <t>`page.get_by_text("Save Preference").click()`</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr"/>
@@ -4538,17 +4135,17 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>e.4</t>
+          <t>a.4</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Click on 'User Suggested Order Total' to select this measure.</t>
+          <t>Reopen the preference dropdown menu to access the options again. Locate the dropdown menu icon and click it.</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("User Suggested Order Total").first.click()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr"/>
@@ -4558,17 +4155,17 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>f.1</t>
+          <t>a.5</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Click on the second instance of 'User Suggested Order Base' to select this measure.</t>
+          <t>Reset the settings to their default state by selecting the 'Reset Preference' option from the dropdown menu.</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("User Suggested Order Base").nth(1).click()`</t>
+          <t>`page.get_by_text("Reset Preference").click()`</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr"/>
@@ -4576,39 +4173,26 @@
       <c r="F206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="3" t="inlineStr">
-        <is>
-          <t>f.2</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>Click on the second instance of 'User Suggested Order Promotion' to select this measure.</t>
-        </is>
-      </c>
-      <c r="C207" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("User Suggested Order Promotion").nth(1).click()`</t>
-        </is>
-      </c>
-      <c r="D207" s="3" t="inlineStr"/>
-      <c r="E207" s="4" t="inlineStr"/>
-      <c r="F207" s="4" t="inlineStr"/>
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>--- PAGINATION INTERACTION AND NAVIGATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>f.3</t>
+          <t>b.1</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Click on the second instance of 'User Override Total' to select this measure.</t>
+          <t>Click on the text 'Showing 10 out of 28 123Rows' to interact with the pagination display.</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("User Override Total").nth(1).click()`</t>
+          <t>`page.get_by_text("Showing 10 out of 28 123Rows").click()`</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr"/>
@@ -4618,17 +4202,17 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>f.4</t>
+          <t>b.2</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Click on the second instance of 'User Override Base' to select this measure.</t>
+          <t>Click on the 'Rows per page View 10 row(s)' dropdown to open the options for changing the number of rows displayed.</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("User Override Base").nth(1).click()`</t>
+          <t>`page.get_by_text("Rows per page View 10 row(s)").click()`</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr"/>
@@ -4638,17 +4222,17 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>g.1</t>
+          <t>b.3</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Click on the first checkbox to select or toggle it.</t>
+          <t>Click on the option 'View 10 row(s)' to confirm the selection of 10 rows per page.</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
+          <t>`page.locator("span").filter(has_text=re.compile(r"^View 10 row\(s\)$")).click()`</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr"/>
@@ -4658,17 +4242,17 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>g.2</t>
+          <t>b.4</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Click on the first checkbox again, possibly to toggle or confirm the selection.</t>
+          <t>Click on the text 'Showing 10 out of' to refresh or interact with the pagination display.</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
+          <t>`page.get_by_text("Showing 10 out of").click()`</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr"/>
@@ -4678,17 +4262,17 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>g.3</t>
+          <t>b.5</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Click on the first checkbox again, possibly to toggle or confirm the selection.</t>
+          <t>Click on the first instance of 'View 10 row(s)' to ensure the selection of 10 rows per page.</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
+          <t>`page.get_by_text("View 10 row(s)").first.click()`</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr"/>
@@ -4698,17 +4282,17 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>h.1</t>
+          <t>b.6</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Click on the second instance of 'ION Suggested Order Promotion' to select this measure.</t>
+          <t>Click on the first instance of 'View 20 row(s)' to change the number of rows displayed to 20.</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("ION Suggested Order Promotion").nth(1).click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^View 20 row\(s\)$")).first.click()`</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr"/>
@@ -4718,17 +4302,17 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>h.2</t>
+          <t>b.7</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Gross Units (CW-4)' to select this measure.</t>
+          <t>Click on the text 'Showing 20 out of' to interact with the updated pagination display.</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Gross Units (CW-4)", exact=True).click()`</t>
+          <t>`page.get_by_text("Showing 20 out of").click()`</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr"/>
@@ -4738,17 +4322,17 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>h.3</t>
+          <t>b.8</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Click on the second instance of 'Gross Units (CW-3)' to select this measure.</t>
+          <t>Click on the exact text '12' to navigate to page 12 in the pagination.</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Gross Units (CW-3)").nth(1).click()`</t>
+          <t>`page.get_by_text("12", exact=True).click()`</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr"/>
@@ -4758,17 +4342,17 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>h.4</t>
+          <t>b.9</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Click on the second instance of 'Aged Net Units (CW-3)' to select this measure.</t>
+          <t>Click on the link with the text '2' to navigate to page 2 in the pagination.</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Aged Net Units (CW-3)").nth(1).click()`</t>
+          <t>`page.locator("a").filter(has_text="2").click()`</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr"/>
@@ -4778,17 +4362,17 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>i.1</t>
+          <t>b.10</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Click on the first selected dropdown option to deselect or modify the selection.</t>
+          <t>Click on the left chevron icon to navigate to the previous page in the pagination.</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32.p-r-16.selected").first.click()`</t>
+          <t>`page.locator(".zeb-chevron-left").click()`</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr"/>
@@ -4798,17 +4382,17 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>i.2</t>
+          <t>b.11</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Click on the first selected dropdown option again, possibly to confirm the deselection or modification.</t>
+          <t>Click on the exact text '12' again to navigate back to page 12.</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32.p-r-16.selected").first.click()`</t>
+          <t>`page.get_by_text("12", exact=True).click()`</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr"/>
@@ -4818,17 +4402,17 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>j.1</t>
+          <t>b.12</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Click on the first checkbox to select or toggle it again.</t>
+          <t>Click on the exact text '12' once more to confirm navigation to page 12.</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
+          <t>`page.get_by_text("12", exact=True).click()`</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr"/>
@@ -4838,17 +4422,17 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>j.2</t>
+          <t>b.13</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Click on the first checkbox again, possibly to toggle or confirm the selection.</t>
+          <t>Click on the 'pagination-last' button to navigate to the last page in the pagination.</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
+          <t>`page.locator(".pagination-last").click()`</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr"/>
@@ -4858,17 +4442,17 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>k.1</t>
+          <t>b.14</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Aged Net Units (CW-6)' to select this measure from the list.</t>
+          <t>Click on the 'zeb-nav-to-first' button to navigate back to the first page in the pagination.</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Aged Net Units (CW-6)", exact=True).click()`</t>
+          <t>`page.locator(".zeb-nav-to-first").click()`</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr"/>
@@ -4876,39 +4460,26 @@
       <c r="F221" s="4" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="3" t="inlineStr">
-        <is>
-          <t>k.2</t>
-        </is>
-      </c>
-      <c r="B222" s="4" t="inlineStr">
-        <is>
-          <t>Click on the first selected dropdown option to deselect or modify the current selection.</t>
-        </is>
-      </c>
-      <c r="C222" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32.p-r-16.selected").first.click()`</t>
-        </is>
-      </c>
-      <c r="D222" s="3" t="inlineStr"/>
-      <c r="E222" s="4" t="inlineStr"/>
-      <c r="F222" s="4" t="inlineStr"/>
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>--- ROW SELECTION AND CARD INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>k.3</t>
+          <t>c.1</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Scan Units (CW-4)' to select this measure from the list.</t>
+          <t>Check the checkbox in the row labeled 'Press Space to toggle row selection (unchecked)' to select the row for 'THOMAS BRANDS'.</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Scan Units (CW-4)", exact=True).click()`</t>
+          <t>`page.get_by_role("row", name="Press Space to toggle row selection (unchecked)  THOMAS BRANDS").get_by_label("Press Space to toggle row").check()`</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr"/>
@@ -4918,17 +4489,17 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>k.4</t>
+          <t>c.2</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Scan Units (CW-4)' again, possibly to confirm or toggle the selection.</t>
+          <t>Click on the card content area to interact with the main filter and summary section.</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Scan Units (CW-4)", exact=True).click()`</t>
+          <t>`page.locator(".card-content.p-24").click()`</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr"/>
@@ -4936,39 +4507,26 @@
       <c r="F224" s="4" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="3" t="inlineStr">
-        <is>
-          <t>l.1</t>
-        </is>
-      </c>
-      <c r="B225" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 21st child element within the overflow container to select a specific option.</t>
-        </is>
-      </c>
-      <c r="C225" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(21)").click()`</t>
-        </is>
-      </c>
-      <c r="D225" s="3" t="inlineStr"/>
-      <c r="E225" s="4" t="inlineStr"/>
-      <c r="F225" s="4" t="inlineStr"/>
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>--- FILTER APPLICATION AND SUMMARY INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>l.2</t>
+          <t>d.1</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>Click on the 20th child element with the specified class to select another option.</t>
+          <t>Click on the text 'FilterTime Latest Order &amp;' to open the filter options.</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(20) &gt; .d-flex").click()`</t>
+          <t>`page.get_by_text("FilterTime Latest Order &amp;").click()`</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr"/>
@@ -4978,17 +4536,17 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>m.1</t>
+          <t>d.2</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Click on the first instance of 'Scan Units (CW-4)' to select this measure.</t>
+          <t>Click on the 'Filter' button to apply or modify the filter settings.</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Scan Units (CW-4)").first.click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Filter$")).click()`</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
@@ -4998,17 +4556,17 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>m.2</t>
+          <t>d.3</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>Click on the first instance of 'Scan Units (CW-4)' again, possibly to confirm or toggle the selection.</t>
+          <t>Click on the 'Time' option to select the time-based filter.</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Scan Units (CW-4)").first.click()`</t>
+          <t>`page.get_by_text("Time").click()`</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr"/>
@@ -5018,17 +4576,17 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>m.3</t>
+          <t>d.4</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Select All' to select all available measures in the dropdown.</t>
+          <t>Click on 'Latest Order &amp; Plan Week' to apply this specific filter.</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Select All").click()`</t>
+          <t>`page.get_by_text("Latest Order &amp; Plan Week").first.click()`</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr"/>
@@ -5038,17 +4596,17 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>n.1</t>
+          <t>d.5</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>Click on the fourth instance of the 'All' text to select or interact with it.</t>
+          <t>Click on 'Daily Summary Product:THOMAS' to view the daily summary for the product 'THOMAS'.</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("All").nth(4).click()`</t>
+          <t>`page.get_by_text("Daily Summary Product:THOMAS").click()`</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr"/>
@@ -5058,17 +4616,17 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>n.2</t>
+          <t>d.6</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Click on the button within the 'Daily Summary Product:THOMAS' card to expand or interact with it.</t>
+          <t>Click on 'Daily Summary' to interact with the summary section.</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Daily Summary Product:THOMAS").get_by_role("button").click()`</t>
+          <t>`page.get_by_text("Daily Summary").click()`</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr"/>
@@ -5078,17 +4636,17 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>o.1</t>
+          <t>d.7</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Filter Columns Input' textbox to focus on it.</t>
+          <t>Click on 'Product:THOMAS BRANDS' to focus on the product-specific summary.</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
+          <t>`page.get_by_text("Product:THOMAS BRANDS").first.click()`</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr"/>
@@ -5098,17 +4656,17 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>o.2</t>
+          <t>d.8</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Fill the 'Filter Columns Input' textbox with the value '02/1' to filter columns based on this input.</t>
+          <t>Click on the third instance of the exact text 'Product' to refine the selection.</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("02/1")`</t>
+          <t>`page.get_by_text("Product", exact=True).nth(2).click()`</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr"/>
@@ -5118,17 +4676,17 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>o.3</t>
+          <t>d.9</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>Click on the first column in the filtered list to select it.</t>
+          <t>Click on the second instance of 'THOMAS BRANDS' to confirm the selection of this product.</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#ag-4958 &gt; .ag-column-panel &gt; .ag-column-select &gt; .ag-column-select-list &gt; .ag-virtual-list-viewport &gt; .ag-virtual-list-container &gt; div &gt; .ag-column-select-column").first.click()`</t>
+          <t>`page.get_by_text("THOMAS BRANDS").nth(1).click()`</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr"/>
@@ -5138,17 +4696,17 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>p.1</t>
+          <t>d.10</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the visibility toggle for the '/11(Wed) Column' to hide it.</t>
+          <t>Click on 'Daily Summary Product:THOMAS' again to refresh or interact with the summary.</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/11(Wed) Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
+          <t>`page.get_by_text("Daily Summary Product:THOMAS").click()`</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr"/>
@@ -5156,39 +4714,26 @@
       <c r="F235" s="4" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="3" t="inlineStr">
-        <is>
-          <t>q.1</t>
-        </is>
-      </c>
-      <c r="B236" s="4" t="inlineStr">
-        <is>
-          <t>Uncheck the visibility toggle for the '/12(Thu) Column' to hide it.</t>
-        </is>
-      </c>
-      <c r="C236" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="/12(Thu) Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
-        </is>
-      </c>
-      <c r="D236" s="3" t="inlineStr"/>
-      <c r="E236" s="4" t="inlineStr"/>
-      <c r="F236" s="4" t="inlineStr"/>
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>--- DROPDOWN INTERACTION AND MEASURE SELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>q.2</t>
+          <t>e.1</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible.</t>
+          <t>Click on the dropdown to open the multiselect options for filtering.</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100").click()`</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr"/>
@@ -5198,17 +4743,17 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>q.3</t>
+          <t>e.2</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Filter Columns Input' textbox again to focus on it.</t>
+          <t>Select the first option in the dropdown list.</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
+          <t>`page.locator(".d-flex.dropdown-option").first.click()`</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr"/>
@@ -5218,17 +4763,17 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>q.4</t>
+          <t>e.3</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Clear the 'Filter Columns Input' textbox by filling it with an empty string.</t>
+          <t>Select the first option in the dropdown list again, possibly to toggle or confirm the selection.</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("")`</t>
+          <t>`page.locator(".d-flex.dropdown-option").first.click()`</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr"/>
@@ -5238,17 +4783,17 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>q.5</t>
+          <t>e.4</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>Press 'Enter' in the 'Filter Columns Input' textbox to apply the filter or finalize the action.</t>
+          <t>Click on 'User Suggested Order Total' to select this measure.</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").press("Enter")`</t>
+          <t>`page.get_by_text("User Suggested Order Total").first.click()`</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr"/>
@@ -5256,39 +4801,26 @@
       <c r="F240" s="4" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="3" t="inlineStr">
-        <is>
-          <t>r.1</t>
-        </is>
-      </c>
-      <c r="B241" s="4" t="inlineStr">
-        <is>
-          <t>Locate the 'Daily Summary Product:THOMAS' card and click the button inside it to expand or interact with the card.</t>
-        </is>
-      </c>
-      <c r="C241" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Daily Summary Product:THOMAS").get_by_role("button").click()`</t>
-        </is>
-      </c>
-      <c r="D241" s="3" t="inlineStr"/>
-      <c r="E241" s="4" t="inlineStr"/>
-      <c r="F241" s="4" t="inlineStr"/>
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>--- MEASURE SELECTION - USER SUGGESTED AND OVERRIDE ---</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>r.2</t>
+          <t>f.1</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>Click the button inside the 'Daily Summary Product:THOMAS' card again to toggle or confirm the action.</t>
+          <t>Click on the second instance of 'User Suggested Order Base' to select this measure.</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Daily Summary Product:THOMAS").get_by_role("button").click()`</t>
+          <t>`page.get_by_text("User Suggested Order Base").nth(1).click()`</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr"/>
@@ -5298,17 +4830,17 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>s.1</t>
+          <t>f.2</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Locate the visibility toggle for the '/01(Sun) Column' and check it to make the column visible.</t>
+          <t>Click on the second instance of 'User Suggested Order Promotion' to select this measure.</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/01(Sun) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_text("User Suggested Order Promotion").nth(1).click()`</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr"/>
@@ -5318,17 +4850,17 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>s.2</t>
+          <t>f.3</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>Locate the visibility toggle for the '/02(Mon) Column' and check it to make the column visible.</t>
+          <t>Click on the second instance of 'User Override Total' to select this measure.</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/02(Mon) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_text("User Override Total").nth(1).click()`</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr"/>
@@ -5338,17 +4870,17 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>s.3</t>
+          <t>f.4</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Locate the visibility toggle for the '/03(Tue) Column' and check it to make the column visible.</t>
+          <t>Click on the second instance of 'User Override Base' to select this measure.</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/03(Tue) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_text("User Override Base").nth(1).click()`</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr"/>
@@ -5356,39 +4888,26 @@
       <c r="F245" s="4" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="3" t="inlineStr">
-        <is>
-          <t>s.4</t>
-        </is>
-      </c>
-      <c r="B246" s="4" t="inlineStr">
-        <is>
-          <t>Locate the visibility toggle for the '/04(Wed) Column' and check it to make the column visible.</t>
-        </is>
-      </c>
-      <c r="C246" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="/04(Wed) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
-        </is>
-      </c>
-      <c r="D246" s="3" t="inlineStr"/>
-      <c r="E246" s="4" t="inlineStr"/>
-      <c r="F246" s="4" t="inlineStr"/>
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>--- CHECKBOX INTERACTION - INITIAL TOGGLES ---</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>s.5</t>
+          <t>g.1</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Locate the visibility toggle for the '/05(Thu) Column' and check it to make the column visible.</t>
+          <t>Click on the first checkbox to select or toggle it.</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/05(Thu) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
@@ -5398,17 +4917,17 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>s.6</t>
+          <t>g.2</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Locate the visibility toggle for the '/06(Fri) Column' and check it to make the column visible.</t>
+          <t>Click on the first checkbox again, possibly to toggle or confirm the selection.</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/06(Fri) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr"/>
@@ -5418,17 +4937,17 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>s.7</t>
+          <t>g.3</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Locate the visibility toggle for the '/07(Sat) Column' and check it to make the column visible.</t>
+          <t>Click on the first checkbox again, possibly to toggle or confirm the selection.</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/07(Sat) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr"/>
@@ -5436,39 +4955,26 @@
       <c r="F249" s="4" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="3" t="inlineStr">
-        <is>
-          <t>s.8</t>
-        </is>
-      </c>
-      <c r="B250" s="4" t="inlineStr">
-        <is>
-          <t>Locate the visibility toggle for the '/08(Sun) Column' and check it to make the column visible.</t>
-        </is>
-      </c>
-      <c r="C250" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="/08(Sun) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
-        </is>
-      </c>
-      <c r="D250" s="3" t="inlineStr"/>
-      <c r="E250" s="4" t="inlineStr"/>
-      <c r="F250" s="4" t="inlineStr"/>
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>--- MEASURE SELECTION - ION SUGGESTED AND GROSS UNITS ---</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>s.9</t>
+          <t>h.1</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Locate the visibility toggle for the '/09(Mon) Column' and check it to make the column visible.</t>
+          <t>Click on the second instance of 'ION Suggested Order Promotion' to select this measure.</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/09(Mon) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_text("ION Suggested Order Promotion").nth(1).click()`</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr"/>
@@ -5478,17 +4984,17 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>s.10</t>
+          <t>h.2</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>Click on the column element located at 'div:nth-child(10) &gt; .ag-column-select-column' to interact with it.</t>
+          <t>Click on 'Gross Units (CW-4)' to select this measure.</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(10) &gt; .ag-column-select-column").click()`</t>
+          <t>`page.get_by_text("Gross Units (CW-4)", exact=True).click()`</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr"/>
@@ -5498,17 +5004,17 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>s.11</t>
+          <t>h.3</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Locate the visibility toggle for the '/11(Wed) Column' and check it to make the column visible.</t>
+          <t>Click on the second instance of 'Gross Units (CW-3)' to select this measure.</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/11(Wed) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_text("Gross Units (CW-3)").nth(1).click()`</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr"/>
@@ -5518,17 +5024,17 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>s.12</t>
+          <t>h.4</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>Locate the visibility toggle for the '/12(Thu) Column' and check it to make the column visible.</t>
+          <t>Click on the second instance of 'Aged Net Units (CW-3)' to select this measure.</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/12(Thu) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_text("Aged Net Units (CW-3)").nth(1).click()`</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr"/>
@@ -5536,39 +5042,26 @@
       <c r="F254" s="4" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="3" t="inlineStr">
-        <is>
-          <t>s.13</t>
-        </is>
-      </c>
-      <c r="B255" s="4" t="inlineStr">
-        <is>
-          <t>Locate the visibility toggle for the '/13(Fri) Column' and check it to make the column visible.</t>
-        </is>
-      </c>
-      <c r="C255" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="/13(Fri) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
-        </is>
-      </c>
-      <c r="D255" s="3" t="inlineStr"/>
-      <c r="E255" s="4" t="inlineStr"/>
-      <c r="F255" s="4" t="inlineStr"/>
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>--- DROPDOWN INTERACTION - DESELECT AND MODIFY ---</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>t.1</t>
+          <t>i.1</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Locate the 'Toggle All Columns Visibility' checkbox and check it to make all columns visible.</t>
+          <t>Click on the first selected dropdown option to deselect or modify the selection.</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32.p-r-16.selected").first.click()`</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr"/>
@@ -5578,17 +5071,17 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>u.1</t>
+          <t>i.2</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Locate the 'Daily Summary Product:THOMAS' card and click the button inside it to expand or interact with the card.</t>
+          <t>Click on the first selected dropdown option again, possibly to confirm the deselection or modification.</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-card-component").filter(has_text="Daily Summary Product:THOMAS").get_by_role("button").click()`</t>
+          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32.p-r-16.selected").first.click()`</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr"/>
@@ -5596,39 +5089,26 @@
       <c r="F257" s="4" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="3" t="inlineStr">
-        <is>
-          <t>v.1</t>
-        </is>
-      </c>
-      <c r="B258" s="4" t="inlineStr">
-        <is>
-          <t>Click on the export icon located in the toolbar to initiate the export process.</t>
-        </is>
-      </c>
-      <c r="C258" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("span:nth-child(6) &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div:nth-child(2) &gt; #export-iconId &gt; .icon-color-toolbar-active").click()`</t>
-        </is>
-      </c>
-      <c r="D258" s="3" t="inlineStr"/>
-      <c r="E258" s="4" t="inlineStr"/>
-      <c r="F258" s="4" t="inlineStr"/>
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>--- CHECKBOX INTERACTION - ADDITIONAL TOGGLES ---</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>v.2</t>
+          <t>j.1</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Click on the text element that provides information about the export limit to proceed with the export process.</t>
+          <t>Click on the first checkbox to select or toggle it again.</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Please note that a maximum of").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
@@ -5638,17 +5118,17 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>w.1</t>
+          <t>j.2</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Click on the preference icon located in the toolbar to open the preferences dropdown menu.</t>
+          <t>Click on the first checkbox again, possibly to toggle or confirm the selection.</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span:nth-child(6) &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr"/>
@@ -5656,39 +5136,26 @@
       <c r="F260" s="4" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="3" t="inlineStr">
-        <is>
-          <t>w.2</t>
-        </is>
-      </c>
-      <c r="B261" s="4" t="inlineStr">
-        <is>
-          <t>Select the 'Save Preference' option from the dropdown menu to save the current preferences.</t>
-        </is>
-      </c>
-      <c r="C261" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Save Preference$")).first.click()`</t>
-        </is>
-      </c>
-      <c r="D261" s="3" t="inlineStr"/>
-      <c r="E261" s="4" t="inlineStr"/>
-      <c r="F261" s="4" t="inlineStr"/>
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>--- MEASURE SELECTION - AGED NET UNITS AND SCAN UNITS ---</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>w.3</t>
+          <t>k.1</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>Click on the preference icon again to reopen the preferences dropdown menu.</t>
+          <t>Click on 'Aged Net Units (CW-6)' to select this measure from the list.</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span:nth-child(6) &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.get_by_text("Aged Net Units (CW-6)", exact=True).click()`</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr"/>
@@ -5698,17 +5165,17 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>w.4</t>
+          <t>k.2</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Reset Preference' option from the dropdown menu to reset the preferences to their default values.</t>
+          <t>Click on the first selected dropdown option to deselect or modify the current selection.</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Reset Preference$")).first.click()`</t>
+          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32.p-r-16.selected").first.click()`</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr"/>
@@ -5718,17 +5185,17 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>x.1</t>
+          <t>k.3</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Click on the header cell to interact with the first column in the grid.</t>
+          <t>Click on 'Scan Units (CW-4)' to select this measure from the list.</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-header-cell.ag-column-first.ag-header-parent-hidden.ag-header-background.ag-focus-managed.ag-header-active &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container &gt; .ag-header-cell-label").click()`</t>
+          <t>`page.get_by_text("Scan Units (CW-4)", exact=True).click()`</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr"/>
@@ -5738,17 +5205,17 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>x.2</t>
+          <t>k.4</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'User Suggested Order Total' text to select or interact with it.</t>
+          <t>Click on 'Scan Units (CW-4)' again, possibly to confirm or toggle the selection.</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("User Suggested Order Total").click()`</t>
+          <t>`page.get_by_text("Scan Units (CW-4)", exact=True).click()`</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr"/>
@@ -5756,39 +5223,26 @@
       <c r="F265" s="4" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="3" t="inlineStr">
-        <is>
-          <t>x.3</t>
-        </is>
-      </c>
-      <c r="B266" s="4" t="inlineStr">
-        <is>
-          <t>Click on the first icon within the grid, possibly to open a filter or perform an action.</t>
-        </is>
-      </c>
-      <c r="C266" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("i").first.click()`</t>
-        </is>
-      </c>
-      <c r="D266" s="3" t="inlineStr"/>
-      <c r="E266" s="4" t="inlineStr"/>
-      <c r="F266" s="4" t="inlineStr"/>
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>--- CHILD ELEMENT SELECTION - OVERFLOW CONTAINER ---</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>x.4</t>
+          <t>l.1</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'User Override Total' text to select or interact with it.</t>
+          <t>Click on the 21st child element within the overflow container to select a specific option.</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("User Override Total").click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(21)").click()`</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr"/>
@@ -5798,17 +5252,17 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>x.5</t>
+          <t>l.2</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>Click on the grid cell labeled 'User Override Total' to interact with it.</t>
+          <t>Click on the 20th child element with the specified class to select another option.</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("gridcell", name=" User Override Total").click()`</t>
+          <t>`page.locator("div:nth-child(20) &gt; .d-flex").click()`</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr"/>
@@ -5816,39 +5270,26 @@
       <c r="F268" s="4" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="3" t="inlineStr">
-        <is>
-          <t>x.6</t>
-        </is>
-      </c>
-      <c r="B269" s="4" t="inlineStr">
-        <is>
-          <t>Click on the second icon within the grid, possibly to open a filter or perform an action.</t>
-        </is>
-      </c>
-      <c r="C269" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("i").nth(2).click()`</t>
-        </is>
-      </c>
-      <c r="D269" s="3" t="inlineStr"/>
-      <c r="E269" s="4" t="inlineStr"/>
-      <c r="F269" s="4" t="inlineStr"/>
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>--- MEASURE SELECTION - SCAN UNITS AND SELECT ALL ---</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>x.7</t>
+          <t>m.1</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Gross Units (CW-3)' text within the grid to select or interact with it.</t>
+          <t>Click on the first instance of 'Scan Units (CW-4)' to select this measure.</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-column-dimentional-grid").get_by_text("Gross Units (CW-3)").click()`</t>
+          <t>`page.get_by_text("Scan Units (CW-4)").first.click()`</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
@@ -5858,17 +5299,17 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>y.1</t>
+          <t>m.2</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Click on the fifth icon within the grid, possibly to open a filter or perform an action.</t>
+          <t>Click on the first instance of 'Scan Units (CW-4)' again, possibly to confirm or toggle the selection.</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("i").nth(5).click()`</t>
+          <t>`page.get_by_text("Scan Units (CW-4)").first.click()`</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
@@ -5878,17 +5319,17 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>y.2</t>
+          <t>m.3</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Aged Net Units (CW-3)' text within the grid to select or interact with it.</t>
+          <t>Click on 'Select All' to select all available measures in the dropdown.</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-column-dimentional-grid").get_by_text("Aged Net Units (CW-3)").click()`</t>
+          <t>`page.get_by_text("Select All").click()`</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
@@ -5896,39 +5337,26 @@
       <c r="F272" s="4" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="3" t="inlineStr">
-        <is>
-          <t>y.3</t>
-        </is>
-      </c>
-      <c r="B273" s="4" t="inlineStr">
-        <is>
-          <t>Click on the chevron icon to expand or collapse a group within the grid.</t>
-        </is>
-      </c>
-      <c r="C273" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".ag-cell-value.ag-cell.ag-cell-not-inline-editing.ag-cell-normal-height.ag-cell-last-left-pinned.ag-column-first.ag-cell-override-normal.notosans-overwrite.no-border.ag-cell-focus &gt; .ag-cell-wrapper &gt; .ag-group-contracted &gt; .zeb-chevron-right").click()`</t>
-        </is>
-      </c>
-      <c r="D273" s="3" t="inlineStr"/>
-      <c r="E273" s="4" t="inlineStr"/>
-      <c r="F273" s="4" t="inlineStr"/>
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>--- INTERACTION WITH 'ALL' AND DAILY SUMMARY CARD ---</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>y.4</t>
+          <t>n.1</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Scan Units (CW-3)' text within the grid to select or interact with it.</t>
+          <t>Click on the fourth instance of the 'All' text to select or interact with it.</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("esp-column-dimentional-grid").get_by_text("Scan Units (CW-3)").click()`</t>
+          <t>`page.get_by_text("All").nth(4).click()`</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
@@ -5938,17 +5366,17 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>y.5</t>
+          <t>n.2</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Click on the chevron icon again to expand or collapse another group within the grid.</t>
+          <t>Click on the button within the 'Daily Summary Product:THOMAS' card to expand or interact with it.</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-cell-value.ag-cell.ag-cell-not-inline-editing.ag-cell-normal-height.ag-cell-last-left-pinned.ag-column-first.ag-cell-override-normal.notosans-overwrite.no-border.ag-cell-focus &gt; .ag-cell-wrapper &gt; .ag-group-contracted &gt; .zeb-chevron-right").click()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Daily Summary Product:THOMAS").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr"/>
@@ -5956,39 +5384,26 @@
       <c r="F275" s="4" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="3" t="inlineStr">
-        <is>
-          <t>z.1</t>
-        </is>
-      </c>
-      <c r="B276" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Daily Trend Product:THOMAS' text to navigate or interact with it.</t>
-        </is>
-      </c>
-      <c r="C276" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Daily Trend Product:THOMAS").click()`</t>
-        </is>
-      </c>
-      <c r="D276" s="3" t="inlineStr"/>
-      <c r="E276" s="4" t="inlineStr"/>
-      <c r="F276" s="4" t="inlineStr"/>
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>--- FILTER COLUMNS INPUT AND COLUMN SELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>z.2</t>
+          <t>o.1</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Daily Trend' text to navigate or interact with it.</t>
+          <t>Click on the 'Filter Columns Input' textbox to focus on it.</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Daily Trend").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr"/>
@@ -5998,17 +5413,17 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>z.3</t>
+          <t>o.2</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Product:THOMAS BRANDS' text within the line-bar chart to interact with it.</t>
+          <t>Fill the 'Filter Columns Input' textbox with the value '02/1' to filter columns based on this input.</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("dp-line-bar-chart").get_by_text("Product:THOMAS BRANDS").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("02/1")`</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr"/>
@@ -6018,17 +5433,17 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>z.4</t>
+          <t>o.3</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Product' text within the line-bar chart to interact with it.</t>
+          <t>Click on the first column in the filtered list to select it.</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("dp-line-bar-chart").get_by_text("Product", exact=True).click()`</t>
+          <t>`page.locator("#ag-4958 &gt; .ag-column-panel &gt; .ag-column-select &gt; .ag-column-select-list &gt; .ag-virtual-list-viewport &gt; .ag-virtual-list-container &gt; div &gt; .ag-column-select-column").first.click()`</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr"/>
@@ -6036,39 +5451,26 @@
       <c r="F279" s="4" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="3" t="inlineStr">
-        <is>
-          <t>z.5</t>
-        </is>
-      </c>
-      <c r="B280" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'THOMAS BRANDS' text within the line-bar chart to interact with it.</t>
-        </is>
-      </c>
-      <c r="C280" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("dp-line-bar-chart").get_by_text("THOMAS BRANDS").click()`</t>
-        </is>
-      </c>
-      <c r="D280" s="3" t="inlineStr"/>
-      <c r="E280" s="4" t="inlineStr"/>
-      <c r="F280" s="4" t="inlineStr"/>
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>--- COLUMN VISIBILITY TOGGLE ---</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>{.1</t>
+          <t>p.1</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret within the multiselect dropdown to open the filter options.</t>
+          <t>Uncheck the visibility toggle for the '/11(Wed) Column' to hide it.</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ellipses &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.get_by_role("treeitem", name="/11(Wed) Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr"/>
@@ -6076,39 +5478,26 @@
       <c r="F281" s="4" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="3" t="inlineStr">
-        <is>
-          <t>{.2</t>
-        </is>
-      </c>
-      <c r="B282" s="4" t="inlineStr">
-        <is>
-          <t>Select the 'User Suggested Order Base' option from the dropdown.</t>
-        </is>
-      </c>
-      <c r="C282" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("span").filter(has_text="User Suggested Order Base").click()`</t>
-        </is>
-      </c>
-      <c r="D282" s="3" t="inlineStr"/>
-      <c r="E282" s="4" t="inlineStr"/>
-      <c r="F282" s="4" t="inlineStr"/>
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>--- COLUMN VISIBILITY MANAGEMENT ---</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>{.3</t>
+          <t>q.1</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Select the 'User Suggested Order Promotion' option from the dropdown.</t>
+          <t>Uncheck the visibility toggle for the '/12(Thu) Column' to hide it.</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span").filter(has_text="User Suggested Order Promotion").click()`</t>
+          <t>`page.get_by_role("treeitem", name="/12(Thu) Column").get_by_label("Press SPACE to toggle visibility (visible)").uncheck()`</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr"/>
@@ -6118,17 +5507,17 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>{.4</t>
+          <t>q.2</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>Select the 'User Override Base' option from the dropdown.</t>
+          <t>Check the 'Toggle All Columns Visibility' checkbox to make all columns visible.</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span").filter(has_text="User Override Base").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr"/>
@@ -6138,17 +5527,17 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>{.5</t>
+          <t>q.3</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Select the 'User Override Promotion' option from the dropdown.</t>
+          <t>Click on the 'Filter Columns Input' textbox again to focus on it.</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("span").filter(has_text="User Override Promotion").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr"/>
@@ -6158,17 +5547,17 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>{.1</t>
+          <t>q.4</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Gross Units (CW-3)' text within the line-bar chart to interact with it.</t>
+          <t>Clear the 'Filter Columns Input' textbox by filling it with an empty string.</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("dp-line-bar-chart span").filter(has_text="Gross Units (CW-3)").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("")`</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr"/>
@@ -6178,17 +5567,17 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>{.2</t>
+          <t>q.5</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Gross Units (CW-4)' text within the line-bar chart to interact with it.</t>
+          <t>Press 'Enter' in the 'Filter Columns Input' textbox to apply the filter or finalize the action.</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("dp-line-bar-chart").get_by_text("Gross Units (CW-4)").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").press("Enter")`</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr"/>
@@ -6196,39 +5585,26 @@
       <c r="F287" s="4" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="3" t="inlineStr">
-        <is>
-          <t>{.3</t>
-        </is>
-      </c>
-      <c r="B288" s="4" t="inlineStr">
-        <is>
-          <t>Click on the seventh element in the grid, possibly to interact with a specific data point or group.</t>
-        </is>
-      </c>
-      <c r="C288" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("div:nth-child(7) &gt; .d-flex").click()`</t>
-        </is>
-      </c>
-      <c r="D288" s="3" t="inlineStr"/>
-      <c r="E288" s="4" t="inlineStr"/>
-      <c r="F288" s="4" t="inlineStr"/>
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>--- DAILY SUMMARY PRODUCT INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>{.4</t>
+          <t>r.1</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Click on the eighth element in the grid, possibly to interact with a specific data point or group.</t>
+          <t>Locate the 'Daily Summary Product:THOMAS' card and click the button inside it to expand or interact with the card.</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(8) &gt; .d-flex").click()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Daily Summary Product:THOMAS").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
@@ -6238,17 +5614,17 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>{.5</t>
+          <t>r.2</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>Click on the ninth element in the grid, possibly to interact with a specific data point or group.</t>
+          <t>Click the button inside the 'Daily Summary Product:THOMAS' card again to toggle or confirm the action.</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(9) &gt; .d-flex").click()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Daily Summary Product:THOMAS").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr"/>
@@ -6256,39 +5632,26 @@
       <c r="F290" s="4" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="3" t="inlineStr">
-        <is>
-          <t>{.6</t>
-        </is>
-      </c>
-      <c r="B291" s="4" t="inlineStr">
-        <is>
-          <t>Click on the tenth element in the grid, possibly to interact with a specific data point or group.</t>
-        </is>
-      </c>
-      <c r="C291" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("div:nth-child(10) &gt; .d-flex").click()`</t>
-        </is>
-      </c>
-      <c r="D291" s="3" t="inlineStr"/>
-      <c r="E291" s="4" t="inlineStr"/>
-      <c r="F291" s="4" t="inlineStr"/>
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>--- TOGGLE INDIVIDUAL COLUMN VISIBILITY ---</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>{.7</t>
+          <t>s.1</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Click on the eleventh element in the grid, possibly to interact with a specific data point or group.</t>
+          <t>Locate the visibility toggle for the '/01(Sun) Column' and check it to make the column visible.</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(11) &gt; .d-flex").click()`</t>
+          <t>`page.get_by_role("treeitem", name="/01(Sun) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
@@ -6298,17 +5661,17 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>{.8</t>
+          <t>s.2</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Click on the twelfth element in the grid, possibly to interact with a specific data point or group.</t>
+          <t>Locate the visibility toggle for the '/02(Mon) Column' and check it to make the column visible.</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(12) &gt; .d-flex").click()`</t>
+          <t>`page.get_by_role("treeitem", name="/02(Mon) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
@@ -6318,17 +5681,17 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>}.1</t>
+          <t>s.3</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Scan Units (CW-3)' text within the line-bar chart to interact with it.</t>
+          <t>Locate the visibility toggle for the '/03(Tue) Column' and check it to make the column visible.</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("dp-line-bar-chart span").filter(has_text="Scan Units (CW-3)").click()`</t>
+          <t>`page.get_by_role("treeitem", name="/03(Tue) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
@@ -6338,17 +5701,17 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>}.2</t>
+          <t>s.4</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Scan Units (CW-4)' text within the line-bar chart to interact with it.</t>
+          <t>Locate the visibility toggle for the '/04(Wed) Column' and check it to make the column visible.</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("dp-line-bar-chart").get_by_text("Scan Units (CW-4)").click()`</t>
+          <t>`page.get_by_role("treeitem", name="/04(Wed) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr"/>
@@ -6358,17 +5721,17 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>}.3</t>
+          <t>s.5</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Scan Units (CW-5)' text within the line-bar chart to interact with it.</t>
+          <t>Locate the visibility toggle for the '/05(Thu) Column' and check it to make the column visible.</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("dp-line-bar-chart").get_by_text("Scan Units (CW-5)").click()`</t>
+          <t>`page.get_by_role("treeitem", name="/05(Thu) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr"/>
@@ -6378,17 +5741,17 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>}.4</t>
+          <t>s.6</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Scan Units (CW-6)' text within the line-bar chart to interact with it.</t>
+          <t>Locate the visibility toggle for the '/06(Fri) Column' and check it to make the column visible.</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("dp-line-bar-chart").get_by_text("Scan Units (CW-6)").click()`</t>
+          <t>`page.get_by_role("treeitem", name="/06(Fri) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr"/>
@@ -6398,17 +5761,17 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>~.1</t>
+          <t>s.7</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Gross Units (CW-4), Gross' text to interact with it, possibly to select or highlight it.</t>
+          <t>Locate the visibility toggle for the '/07(Sat) Column' and check it to make the column visible.</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Gross Units (CW-4), Gross").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="/07(Sat) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
@@ -6418,17 +5781,17 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>~.2</t>
+          <t>s.8</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Click on the multiselect dropdown within the preference icon container to open the preference options.</t>
+          <t>Locate the visibility toggle for the '/08(Sun) Column' and check it to make the column visible.</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".title.d-flex.align-items-center.font-size-16.font-weight-bold.nunito.title-color &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.get_by_role("treeitem", name="/08(Sun) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr"/>
@@ -6438,17 +5801,17 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>~.3</t>
+          <t>s.9</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Save Preference' to save the current settings or selections.</t>
+          <t>Locate the visibility toggle for the '/09(Mon) Column' and check it to make the column visible.</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Save Preference").click()`</t>
+          <t>`page.get_by_role("treeitem", name="/09(Mon) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr"/>
@@ -6458,17 +5821,17 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>~.4</t>
+          <t>s.10</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Click on the multiselect dropdown within the preference icon container again, possibly to access additional options.</t>
+          <t>Click on the column element located at 'div:nth-child(10) &gt; .ag-column-select-column' to interact with it.</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".title.d-flex.align-items-center.font-size-16.font-weight-bold.nunito.title-color &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+          <t>`page.locator("div:nth-child(10) &gt; .ag-column-select-column").click()`</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr"/>
@@ -6478,17 +5841,17 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>~.5</t>
+          <t>s.11</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Reset Preference' to reset the preferences to their default state.</t>
+          <t>Locate the visibility toggle for the '/11(Wed) Column' and check it to make the column visible.</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Reset Preference").click()`</t>
+          <t>`page.get_by_role("treeitem", name="/11(Wed) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr"/>
@@ -6498,17 +5861,17 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>.1</t>
+          <t>s.12</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Click on the element identified by 'path:nth-child(81)', possibly to interact with a specific UI component. The exact purpose is unclear from the locator.</t>
+          <t>Locate the visibility toggle for the '/12(Thu) Column' and check it to make the column visible.</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("path:nth-child(81)").click()`</t>
+          <t>`page.get_by_role("treeitem", name="/12(Thu) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr"/>
@@ -6518,17 +5881,17 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>.2</t>
+          <t>s.13</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'User Override Base' text to select or highlight this option in the table.</t>
+          <t>Locate the visibility toggle for the '/13(Fri) Column' and check it to make the column visible.</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("User Override Base", exact=True).click()`</t>
+          <t>`page.get_by_role("treeitem", name="/13(Fri) Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr"/>
@@ -6536,39 +5899,26 @@
       <c r="F304" s="4" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="3" t="inlineStr">
-        <is>
-          <t>.3</t>
-        </is>
-      </c>
-      <c r="B305" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'User Suggested Order Promotion' text to select or highlight this option in the table.</t>
-        </is>
-      </c>
-      <c r="C305" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("User Suggested Order Promotion", exact=True).click()`</t>
-        </is>
-      </c>
-      <c r="D305" s="3" t="inlineStr"/>
-      <c r="E305" s="4" t="inlineStr"/>
-      <c r="F305" s="4" t="inlineStr"/>
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>--- TOGGLE ALL COLUMNS VISIBILITY ---</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>.4</t>
+          <t>t.1</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'User Override Base' text again, possibly to toggle or reselect this option.</t>
+          <t>Locate the 'Toggle All Columns Visibility' checkbox and check it to make all columns visible.</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("User Override Base", exact=True).click()`</t>
+          <t>`page.get_by_role("checkbox", name="Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr"/>
@@ -6576,39 +5926,26 @@
       <c r="F306" s="4" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="3" t="inlineStr">
-        <is>
-          <t>.5</t>
-        </is>
-      </c>
-      <c r="B307" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'User Suggested Order Promotion' text again, possibly to toggle or reselect this option.</t>
-        </is>
-      </c>
-      <c r="C307" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("User Suggested Order Promotion", exact=True).click()`</t>
-        </is>
-      </c>
-      <c r="D307" s="3" t="inlineStr"/>
-      <c r="E307" s="4" t="inlineStr"/>
-      <c r="F307" s="4" t="inlineStr"/>
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>--- DAILY SUMMARY PRODUCT RE-INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>.1</t>
+          <t>u.1</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>Click on the SVG element, possibly to interact with a chart or graph. The exact purpose is unclear from the locator.</t>
+          <t>Locate the 'Daily Summary Product:THOMAS' card and click the button inside it to expand or interact with the card.</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("svg").click()`</t>
+          <t>`page.locator("esp-card-component").filter(has_text="Daily Summary Product:THOMAS").get_by_role("button").click()`</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr"/>
@@ -6616,39 +5953,26 @@
       <c r="F308" s="4" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="3" t="inlineStr">
-        <is>
-          <t>.2</t>
-        </is>
-      </c>
-      <c r="B309" s="4" t="inlineStr">
-        <is>
-          <t>Click on the SVG element again, likely to perform a secondary interaction with the chart or graph.</t>
-        </is>
-      </c>
-      <c r="C309" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("svg").click()`</t>
-        </is>
-      </c>
-      <c r="D309" s="3" t="inlineStr"/>
-      <c r="E309" s="4" t="inlineStr"/>
-      <c r="F309" s="4" t="inlineStr"/>
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>--- EXPORT PROCESS ---</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>.3</t>
+          <t>v.1</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>Click on the date '02/03/2026' in the chart to select or highlight data associated with this specific date.</t>
+          <t>Click on the export icon located in the toolbar to initiate the export process.</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("02/03/2026", exact=True).click()`</t>
+          <t>`page.locator("span:nth-child(6) &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div:nth-child(2) &gt; #export-iconId &gt; .icon-color-toolbar-active").click()`</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr"/>
@@ -6658,17 +5982,17 @@
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>.4</t>
+          <t>v.2</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Click on the text '300K', likely to select or highlight data associated with this value in the chart.</t>
+          <t>Click on the text element that provides information about the export limit to proceed with the export process.</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("300K").click()`</t>
+          <t>`page.get_by_text("Please note that a maximum of").click()`</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr"/>
@@ -6676,39 +6000,26 @@
       <c r="F311" s="4" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="3" t="inlineStr">
-        <is>
-          <t>.5</t>
-        </is>
-      </c>
-      <c r="B312" s="4" t="inlineStr">
-        <is>
-          <t>Click on the text '600K', likely to select or highlight data associated with this value in the chart.</t>
-        </is>
-      </c>
-      <c r="C312" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("600K").click()`</t>
-        </is>
-      </c>
-      <c r="D312" s="3" t="inlineStr"/>
-      <c r="E312" s="4" t="inlineStr"/>
-      <c r="F312" s="4" t="inlineStr"/>
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>--- PREFERENCE MANAGEMENT ---</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>.6</t>
+          <t>w.1</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Click on the bar chart element corresponding to 'path:nth-child(57)', likely to highlight or interact with a specific data point in the chart.</t>
+          <t>Click on the preference icon located in the toolbar to open the preferences dropdown menu.</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("path:nth-child(57)").click()`</t>
+          <t>`page.locator("span:nth-child(6) &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D313" s="3" t="inlineStr"/>
@@ -6718,17 +6029,17 @@
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>.7</t>
+          <t>w.2</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Repeat the click action on the same bar chart element ('path:nth-child(57)'), possibly to ensure the interaction is registered.</t>
+          <t>Select the 'Save Preference' option from the dropdown menu to save the current preferences.</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("path:nth-child(57)").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Save Preference$")).first.click()`</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr"/>
@@ -6738,17 +6049,17 @@
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t>.8</t>
+          <t>w.3</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Click on the bar chart element corresponding to 'path:nth-child(99)', likely to highlight or interact with another specific data point in the chart.</t>
+          <t>Click on the preference icon again to reopen the preferences dropdown menu.</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("path:nth-child(99)").click()`</t>
+          <t>`page.locator("span:nth-child(6) &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div:nth-child(3) &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr"/>
@@ -6758,26 +6069,1211 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>.9</t>
+          <t>w.4</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>Click on the bar chart element corresponding to 'path:nth-child(98)', likely to highlight or interact with yet another specific data point in the chart.</t>
+          <t>Select the 'Reset Preference' option from the dropdown menu to reset the preferences to their default values.</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("path:nth-child(98)").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Reset Preference$")).first.click()`</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr"/>
       <c r="E316" s="4" t="inlineStr"/>
       <c r="F316" s="4" t="inlineStr"/>
     </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>--- GRID HEADER AND COLUMN INTERACTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>x.1</t>
+        </is>
+      </c>
+      <c r="B318" s="4" t="inlineStr">
+        <is>
+          <t>Click on the header cell to interact with the first column in the grid.</t>
+        </is>
+      </c>
+      <c r="C318" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".ag-header-cell.ag-column-first.ag-header-parent-hidden.ag-header-background.ag-focus-managed.ag-header-active &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container &gt; .ag-header-cell-label").click()`</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr"/>
+      <c r="E318" s="4" t="inlineStr"/>
+      <c r="F318" s="4" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>x.2</t>
+        </is>
+      </c>
+      <c r="B319" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'User Suggested Order Total' text to select or interact with it.</t>
+        </is>
+      </c>
+      <c r="C319" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("User Suggested Order Total").click()`</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr"/>
+      <c r="E319" s="4" t="inlineStr"/>
+      <c r="F319" s="4" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>x.3</t>
+        </is>
+      </c>
+      <c r="B320" s="4" t="inlineStr">
+        <is>
+          <t>Click on the first icon within the grid, possibly to open a filter or perform an action.</t>
+        </is>
+      </c>
+      <c r="C320" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("i").first.click()`</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr"/>
+      <c r="E320" s="4" t="inlineStr"/>
+      <c r="F320" s="4" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>x.4</t>
+        </is>
+      </c>
+      <c r="B321" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'User Override Total' text to select or interact with it.</t>
+        </is>
+      </c>
+      <c r="C321" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("User Override Total").click()`</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr"/>
+      <c r="E321" s="4" t="inlineStr"/>
+      <c r="F321" s="4" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>x.5</t>
+        </is>
+      </c>
+      <c r="B322" s="4" t="inlineStr">
+        <is>
+          <t>Click on the grid cell labeled 'User Override Total' to interact with it.</t>
+        </is>
+      </c>
+      <c r="C322" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("gridcell", name=" User Override Total").click()`</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr"/>
+      <c r="E322" s="4" t="inlineStr"/>
+      <c r="F322" s="4" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>x.6</t>
+        </is>
+      </c>
+      <c r="B323" s="4" t="inlineStr">
+        <is>
+          <t>Click on the second icon within the grid, possibly to open a filter or perform an action.</t>
+        </is>
+      </c>
+      <c r="C323" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("i").nth(2).click()`</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr"/>
+      <c r="E323" s="4" t="inlineStr"/>
+      <c r="F323" s="4" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t>x.7</t>
+        </is>
+      </c>
+      <c r="B324" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Gross Units (CW-3)' text within the grid to select or interact with it.</t>
+        </is>
+      </c>
+      <c r="C324" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("esp-column-dimentional-grid").get_by_text("Gross Units (CW-3)").click()`</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr"/>
+      <c r="E324" s="4" t="inlineStr"/>
+      <c r="F324" s="4" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>--- GRID CHEVRON AND TEXT INTERACTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t>y.1</t>
+        </is>
+      </c>
+      <c r="B326" s="4" t="inlineStr">
+        <is>
+          <t>Click on the fifth icon within the grid, possibly to open a filter or perform an action.</t>
+        </is>
+      </c>
+      <c r="C326" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("i").nth(5).click()`</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr"/>
+      <c r="E326" s="4" t="inlineStr"/>
+      <c r="F326" s="4" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="3" t="inlineStr">
+        <is>
+          <t>y.2</t>
+        </is>
+      </c>
+      <c r="B327" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Aged Net Units (CW-3)' text within the grid to select or interact with it.</t>
+        </is>
+      </c>
+      <c r="C327" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("esp-column-dimentional-grid").get_by_text("Aged Net Units (CW-3)").click()`</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="inlineStr"/>
+      <c r="E327" s="4" t="inlineStr"/>
+      <c r="F327" s="4" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t>y.3</t>
+        </is>
+      </c>
+      <c r="B328" s="4" t="inlineStr">
+        <is>
+          <t>Click on the chevron icon to expand or collapse a group within the grid.</t>
+        </is>
+      </c>
+      <c r="C328" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".ag-cell-value.ag-cell.ag-cell-not-inline-editing.ag-cell-normal-height.ag-cell-last-left-pinned.ag-column-first.ag-cell-override-normal.notosans-overwrite.no-border.ag-cell-focus &gt; .ag-cell-wrapper &gt; .ag-group-contracted &gt; .zeb-chevron-right").click()`</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr"/>
+      <c r="E328" s="4" t="inlineStr"/>
+      <c r="F328" s="4" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t>y.4</t>
+        </is>
+      </c>
+      <c r="B329" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Scan Units (CW-3)' text within the grid to select or interact with it.</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("esp-column-dimentional-grid").get_by_text("Scan Units (CW-3)").click()`</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="inlineStr"/>
+      <c r="E329" s="4" t="inlineStr"/>
+      <c r="F329" s="4" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="3" t="inlineStr">
+        <is>
+          <t>y.5</t>
+        </is>
+      </c>
+      <c r="B330" s="4" t="inlineStr">
+        <is>
+          <t>Click on the chevron icon again to expand or collapse another group within the grid.</t>
+        </is>
+      </c>
+      <c r="C330" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".ag-cell-value.ag-cell.ag-cell-not-inline-editing.ag-cell-normal-height.ag-cell-last-left-pinned.ag-column-first.ag-cell-override-normal.notosans-overwrite.no-border.ag-cell-focus &gt; .ag-cell-wrapper &gt; .ag-group-contracted &gt; .zeb-chevron-right").click()`</t>
+        </is>
+      </c>
+      <c r="D330" s="3" t="inlineStr"/>
+      <c r="E330" s="4" t="inlineStr"/>
+      <c r="F330" s="4" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>--- DAILY TREND AND LINE-BAR CHART INTERACTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t>z.1</t>
+        </is>
+      </c>
+      <c r="B332" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Daily Trend Product:THOMAS' text to navigate or interact with it.</t>
+        </is>
+      </c>
+      <c r="C332" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Daily Trend Product:THOMAS").click()`</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="inlineStr"/>
+      <c r="E332" s="4" t="inlineStr"/>
+      <c r="F332" s="4" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>z.2</t>
+        </is>
+      </c>
+      <c r="B333" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Daily Trend' text to navigate or interact with it.</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Daily Trend").click()`</t>
+        </is>
+      </c>
+      <c r="D333" s="3" t="inlineStr"/>
+      <c r="E333" s="4" t="inlineStr"/>
+      <c r="F333" s="4" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>z.3</t>
+        </is>
+      </c>
+      <c r="B334" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Product:THOMAS BRANDS' text within the line-bar chart to interact with it.</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("dp-line-bar-chart").get_by_text("Product:THOMAS BRANDS").click()`</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr"/>
+      <c r="E334" s="4" t="inlineStr"/>
+      <c r="F334" s="4" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>z.4</t>
+        </is>
+      </c>
+      <c r="B335" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Product' text within the line-bar chart to interact with it.</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("dp-line-bar-chart").get_by_text("Product", exact=True).click()`</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr"/>
+      <c r="E335" s="4" t="inlineStr"/>
+      <c r="F335" s="4" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>z.5</t>
+        </is>
+      </c>
+      <c r="B336" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'THOMAS BRANDS' text within the line-bar chart to interact with it.</t>
+        </is>
+      </c>
+      <c r="C336" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("dp-line-bar-chart").get_by_text("THOMAS BRANDS").click()`</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr"/>
+      <c r="E336" s="4" t="inlineStr"/>
+      <c r="F336" s="4" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>--- DROPDOWN AND FILTER SELECTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t>{.1</t>
+        </is>
+      </c>
+      <c r="B338" s="4" t="inlineStr">
+        <is>
+          <t>Click on the dropdown caret within the multiselect dropdown to open the filter options.</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".ellipses &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="inlineStr"/>
+      <c r="E338" s="4" t="inlineStr"/>
+      <c r="F338" s="4" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>{.2</t>
+        </is>
+      </c>
+      <c r="B339" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'User Suggested Order Base' option from the dropdown.</t>
+        </is>
+      </c>
+      <c r="C339" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("span").filter(has_text="User Suggested Order Base").click()`</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="inlineStr"/>
+      <c r="E339" s="4" t="inlineStr"/>
+      <c r="F339" s="4" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="3" t="inlineStr">
+        <is>
+          <t>{.3</t>
+        </is>
+      </c>
+      <c r="B340" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'User Suggested Order Promotion' option from the dropdown.</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("span").filter(has_text="User Suggested Order Promotion").click()`</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="inlineStr"/>
+      <c r="E340" s="4" t="inlineStr"/>
+      <c r="F340" s="4" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="3" t="inlineStr">
+        <is>
+          <t>{.4</t>
+        </is>
+      </c>
+      <c r="B341" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'User Override Base' option from the dropdown.</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("span").filter(has_text="User Override Base").click()`</t>
+        </is>
+      </c>
+      <c r="D341" s="3" t="inlineStr"/>
+      <c r="E341" s="4" t="inlineStr"/>
+      <c r="F341" s="4" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t>{.5</t>
+        </is>
+      </c>
+      <c r="B342" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'User Override Promotion' option from the dropdown.</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("span").filter(has_text="User Override Promotion").click()`</t>
+        </is>
+      </c>
+      <c r="D342" s="3" t="inlineStr"/>
+      <c r="E342" s="4" t="inlineStr"/>
+      <c r="F342" s="4" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>--- LINE-BAR CHART AND GRID ELEMENT INTERACTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="3" t="inlineStr">
+        <is>
+          <t>{.1</t>
+        </is>
+      </c>
+      <c r="B344" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Gross Units (CW-3)' text within the line-bar chart to interact with it.</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("dp-line-bar-chart span").filter(has_text="Gross Units (CW-3)").click()`</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="inlineStr"/>
+      <c r="E344" s="4" t="inlineStr"/>
+      <c r="F344" s="4" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="3" t="inlineStr">
+        <is>
+          <t>{.2</t>
+        </is>
+      </c>
+      <c r="B345" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Gross Units (CW-4)' text within the line-bar chart to interact with it.</t>
+        </is>
+      </c>
+      <c r="C345" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("dp-line-bar-chart").get_by_text("Gross Units (CW-4)").click()`</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="inlineStr"/>
+      <c r="E345" s="4" t="inlineStr"/>
+      <c r="F345" s="4" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t>{.3</t>
+        </is>
+      </c>
+      <c r="B346" s="4" t="inlineStr">
+        <is>
+          <t>Click on the seventh element in the grid, possibly to interact with a specific data point or group.</t>
+        </is>
+      </c>
+      <c r="C346" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(7) &gt; .d-flex").click()`</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="inlineStr"/>
+      <c r="E346" s="4" t="inlineStr"/>
+      <c r="F346" s="4" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="3" t="inlineStr">
+        <is>
+          <t>{.4</t>
+        </is>
+      </c>
+      <c r="B347" s="4" t="inlineStr">
+        <is>
+          <t>Click on the eighth element in the grid, possibly to interact with a specific data point or group.</t>
+        </is>
+      </c>
+      <c r="C347" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(8) &gt; .d-flex").click()`</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="inlineStr"/>
+      <c r="E347" s="4" t="inlineStr"/>
+      <c r="F347" s="4" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="3" t="inlineStr">
+        <is>
+          <t>{.5</t>
+        </is>
+      </c>
+      <c r="B348" s="4" t="inlineStr">
+        <is>
+          <t>Click on the ninth element in the grid, possibly to interact with a specific data point or group.</t>
+        </is>
+      </c>
+      <c r="C348" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(9) &gt; .d-flex").click()`</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="inlineStr"/>
+      <c r="E348" s="4" t="inlineStr"/>
+      <c r="F348" s="4" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="3" t="inlineStr">
+        <is>
+          <t>{.6</t>
+        </is>
+      </c>
+      <c r="B349" s="4" t="inlineStr">
+        <is>
+          <t>Click on the tenth element in the grid, possibly to interact with a specific data point or group.</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(10) &gt; .d-flex").click()`</t>
+        </is>
+      </c>
+      <c r="D349" s="3" t="inlineStr"/>
+      <c r="E349" s="4" t="inlineStr"/>
+      <c r="F349" s="4" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="3" t="inlineStr">
+        <is>
+          <t>{.7</t>
+        </is>
+      </c>
+      <c r="B350" s="4" t="inlineStr">
+        <is>
+          <t>Click on the eleventh element in the grid, possibly to interact with a specific data point or group.</t>
+        </is>
+      </c>
+      <c r="C350" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(11) &gt; .d-flex").click()`</t>
+        </is>
+      </c>
+      <c r="D350" s="3" t="inlineStr"/>
+      <c r="E350" s="4" t="inlineStr"/>
+      <c r="F350" s="4" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="3" t="inlineStr">
+        <is>
+          <t>{.8</t>
+        </is>
+      </c>
+      <c r="B351" s="4" t="inlineStr">
+        <is>
+          <t>Click on the twelfth element in the grid, possibly to interact with a specific data point or group.</t>
+        </is>
+      </c>
+      <c r="C351" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(12) &gt; .d-flex").click()`</t>
+        </is>
+      </c>
+      <c r="D351" s="3" t="inlineStr"/>
+      <c r="E351" s="4" t="inlineStr"/>
+      <c r="F351" s="4" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>--- INTERACTION WITH LINE-BAR CHART ELEMENTS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="3" t="inlineStr">
+        <is>
+          <t>}.1</t>
+        </is>
+      </c>
+      <c r="B353" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Scan Units (CW-3)' text within the line-bar chart to interact with it.</t>
+        </is>
+      </c>
+      <c r="C353" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("dp-line-bar-chart span").filter(has_text="Scan Units (CW-3)").click()`</t>
+        </is>
+      </c>
+      <c r="D353" s="3" t="inlineStr"/>
+      <c r="E353" s="4" t="inlineStr"/>
+      <c r="F353" s="4" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="3" t="inlineStr">
+        <is>
+          <t>}.2</t>
+        </is>
+      </c>
+      <c r="B354" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Scan Units (CW-4)' text within the line-bar chart to interact with it.</t>
+        </is>
+      </c>
+      <c r="C354" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("dp-line-bar-chart").get_by_text("Scan Units (CW-4)").click()`</t>
+        </is>
+      </c>
+      <c r="D354" s="3" t="inlineStr"/>
+      <c r="E354" s="4" t="inlineStr"/>
+      <c r="F354" s="4" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="3" t="inlineStr">
+        <is>
+          <t>}.3</t>
+        </is>
+      </c>
+      <c r="B355" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Scan Units (CW-5)' text within the line-bar chart to interact with it.</t>
+        </is>
+      </c>
+      <c r="C355" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("dp-line-bar-chart").get_by_text("Scan Units (CW-5)").click()`</t>
+        </is>
+      </c>
+      <c r="D355" s="3" t="inlineStr"/>
+      <c r="E355" s="4" t="inlineStr"/>
+      <c r="F355" s="4" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="3" t="inlineStr">
+        <is>
+          <t>}.4</t>
+        </is>
+      </c>
+      <c r="B356" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Scan Units (CW-6)' text within the line-bar chart to interact with it.</t>
+        </is>
+      </c>
+      <c r="C356" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("dp-line-bar-chart").get_by_text("Scan Units (CW-6)").click()`</t>
+        </is>
+      </c>
+      <c r="D356" s="3" t="inlineStr"/>
+      <c r="E356" s="4" t="inlineStr"/>
+      <c r="F356" s="4" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>--- PREFERENCE MANAGEMENT ACTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="3" t="inlineStr">
+        <is>
+          <t>~.1</t>
+        </is>
+      </c>
+      <c r="B358" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Gross Units (CW-4), Gross' text to interact with it, possibly to select or highlight it.</t>
+        </is>
+      </c>
+      <c r="C358" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Gross Units (CW-4), Gross").first.click()`</t>
+        </is>
+      </c>
+      <c r="D358" s="3" t="inlineStr"/>
+      <c r="E358" s="4" t="inlineStr"/>
+      <c r="F358" s="4" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="3" t="inlineStr">
+        <is>
+          <t>~.2</t>
+        </is>
+      </c>
+      <c r="B359" s="4" t="inlineStr">
+        <is>
+          <t>Click on the multiselect dropdown within the preference icon container to open the preference options.</t>
+        </is>
+      </c>
+      <c r="C359" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".title.d-flex.align-items-center.font-size-16.font-weight-bold.nunito.title-color &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+        </is>
+      </c>
+      <c r="D359" s="3" t="inlineStr"/>
+      <c r="E359" s="4" t="inlineStr"/>
+      <c r="F359" s="4" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="3" t="inlineStr">
+        <is>
+          <t>~.3</t>
+        </is>
+      </c>
+      <c r="B360" s="4" t="inlineStr">
+        <is>
+          <t>Click on 'Save Preference' to save the current settings or selections.</t>
+        </is>
+      </c>
+      <c r="C360" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Save Preference").click()`</t>
+        </is>
+      </c>
+      <c r="D360" s="3" t="inlineStr"/>
+      <c r="E360" s="4" t="inlineStr"/>
+      <c r="F360" s="4" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="3" t="inlineStr">
+        <is>
+          <t>~.4</t>
+        </is>
+      </c>
+      <c r="B361" s="4" t="inlineStr">
+        <is>
+          <t>Click on the multiselect dropdown within the preference icon container again, possibly to access additional options.</t>
+        </is>
+      </c>
+      <c r="C361" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".title.d-flex.align-items-center.font-size-16.font-weight-bold.nunito.title-color &gt; .grid-icons-container &gt; esp-grid-icons-component &gt; .display-grid-icons &gt; div &gt; #preference-iconId &gt; .legend-font &gt; .multiselect-dropdown &gt; .pointer").click()`</t>
+        </is>
+      </c>
+      <c r="D361" s="3" t="inlineStr"/>
+      <c r="E361" s="4" t="inlineStr"/>
+      <c r="F361" s="4" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="3" t="inlineStr">
+        <is>
+          <t>~.5</t>
+        </is>
+      </c>
+      <c r="B362" s="4" t="inlineStr">
+        <is>
+          <t>Click on 'Reset Preference' to reset the preferences to their default state.</t>
+        </is>
+      </c>
+      <c r="C362" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Reset Preference").click()`</t>
+        </is>
+      </c>
+      <c r="D362" s="3" t="inlineStr"/>
+      <c r="E362" s="4" t="inlineStr"/>
+      <c r="F362" s="4" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>--- TABLE ELEMENT INTERACTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="3" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B364" s="4" t="inlineStr">
+        <is>
+          <t>Click on the element identified by 'path:nth-child(81)', possibly to interact with a specific UI component. The exact purpose is unclear from the locator.</t>
+        </is>
+      </c>
+      <c r="C364" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("path:nth-child(81)").click()`</t>
+        </is>
+      </c>
+      <c r="D364" s="3" t="inlineStr"/>
+      <c r="E364" s="4" t="inlineStr"/>
+      <c r="F364" s="4" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="3" t="inlineStr">
+        <is>
+          <t>.2</t>
+        </is>
+      </c>
+      <c r="B365" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'User Override Base' text to select or highlight this option in the table.</t>
+        </is>
+      </c>
+      <c r="C365" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("User Override Base", exact=True).click()`</t>
+        </is>
+      </c>
+      <c r="D365" s="3" t="inlineStr"/>
+      <c r="E365" s="4" t="inlineStr"/>
+      <c r="F365" s="4" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="3" t="inlineStr">
+        <is>
+          <t>.3</t>
+        </is>
+      </c>
+      <c r="B366" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'User Suggested Order Promotion' text to select or highlight this option in the table.</t>
+        </is>
+      </c>
+      <c r="C366" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("User Suggested Order Promotion", exact=True).click()`</t>
+        </is>
+      </c>
+      <c r="D366" s="3" t="inlineStr"/>
+      <c r="E366" s="4" t="inlineStr"/>
+      <c r="F366" s="4" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="3" t="inlineStr">
+        <is>
+          <t>.4</t>
+        </is>
+      </c>
+      <c r="B367" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'User Override Base' text again, possibly to toggle or reselect this option.</t>
+        </is>
+      </c>
+      <c r="C367" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("User Override Base", exact=True).click()`</t>
+        </is>
+      </c>
+      <c r="D367" s="3" t="inlineStr"/>
+      <c r="E367" s="4" t="inlineStr"/>
+      <c r="F367" s="4" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="3" t="inlineStr">
+        <is>
+          <t>.5</t>
+        </is>
+      </c>
+      <c r="B368" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'User Suggested Order Promotion' text again, possibly to toggle or reselect this option.</t>
+        </is>
+      </c>
+      <c r="C368" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("User Suggested Order Promotion", exact=True).click()`</t>
+        </is>
+      </c>
+      <c r="D368" s="3" t="inlineStr"/>
+      <c r="E368" s="4" t="inlineStr"/>
+      <c r="F368" s="4" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>--- CHART AND GRAPH INTERACTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="3" t="inlineStr">
+        <is>
+          <t>.1</t>
+        </is>
+      </c>
+      <c r="B370" s="4" t="inlineStr">
+        <is>
+          <t>Click on the SVG element, possibly to interact with a chart or graph. The exact purpose is unclear from the locator.</t>
+        </is>
+      </c>
+      <c r="C370" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("svg").click()`</t>
+        </is>
+      </c>
+      <c r="D370" s="3" t="inlineStr"/>
+      <c r="E370" s="4" t="inlineStr"/>
+      <c r="F370" s="4" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="3" t="inlineStr">
+        <is>
+          <t>.2</t>
+        </is>
+      </c>
+      <c r="B371" s="4" t="inlineStr">
+        <is>
+          <t>Click on the SVG element again, likely to perform a secondary interaction with the chart or graph.</t>
+        </is>
+      </c>
+      <c r="C371" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("svg").click()`</t>
+        </is>
+      </c>
+      <c r="D371" s="3" t="inlineStr"/>
+      <c r="E371" s="4" t="inlineStr"/>
+      <c r="F371" s="4" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="3" t="inlineStr">
+        <is>
+          <t>.3</t>
+        </is>
+      </c>
+      <c r="B372" s="4" t="inlineStr">
+        <is>
+          <t>Click on the date '02/03/2026' in the chart to select or highlight data associated with this specific date.</t>
+        </is>
+      </c>
+      <c r="C372" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("02/03/2026", exact=True).click()`</t>
+        </is>
+      </c>
+      <c r="D372" s="3" t="inlineStr"/>
+      <c r="E372" s="4" t="inlineStr"/>
+      <c r="F372" s="4" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="3" t="inlineStr">
+        <is>
+          <t>.4</t>
+        </is>
+      </c>
+      <c r="B373" s="4" t="inlineStr">
+        <is>
+          <t>Click on the text '300K', likely to select or highlight data associated with this value in the chart.</t>
+        </is>
+      </c>
+      <c r="C373" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("300K").click()`</t>
+        </is>
+      </c>
+      <c r="D373" s="3" t="inlineStr"/>
+      <c r="E373" s="4" t="inlineStr"/>
+      <c r="F373" s="4" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="3" t="inlineStr">
+        <is>
+          <t>.5</t>
+        </is>
+      </c>
+      <c r="B374" s="4" t="inlineStr">
+        <is>
+          <t>Click on the text '600K', likely to select or highlight data associated with this value in the chart.</t>
+        </is>
+      </c>
+      <c r="C374" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("600K").click()`</t>
+        </is>
+      </c>
+      <c r="D374" s="3" t="inlineStr"/>
+      <c r="E374" s="4" t="inlineStr"/>
+      <c r="F374" s="4" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="3" t="inlineStr">
+        <is>
+          <t>.6</t>
+        </is>
+      </c>
+      <c r="B375" s="4" t="inlineStr">
+        <is>
+          <t>Click on the bar chart element corresponding to 'path:nth-child(57)', likely to highlight or interact with a specific data point in the chart.</t>
+        </is>
+      </c>
+      <c r="C375" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("path:nth-child(57)").click()`</t>
+        </is>
+      </c>
+      <c r="D375" s="3" t="inlineStr"/>
+      <c r="E375" s="4" t="inlineStr"/>
+      <c r="F375" s="4" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="3" t="inlineStr">
+        <is>
+          <t>.7</t>
+        </is>
+      </c>
+      <c r="B376" s="4" t="inlineStr">
+        <is>
+          <t>Repeat the click action on the same bar chart element ('path:nth-child(57)'), possibly to ensure the interaction is registered.</t>
+        </is>
+      </c>
+      <c r="C376" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("path:nth-child(57)").click()`</t>
+        </is>
+      </c>
+      <c r="D376" s="3" t="inlineStr"/>
+      <c r="E376" s="4" t="inlineStr"/>
+      <c r="F376" s="4" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="3" t="inlineStr">
+        <is>
+          <t>.8</t>
+        </is>
+      </c>
+      <c r="B377" s="4" t="inlineStr">
+        <is>
+          <t>Click on the bar chart element corresponding to 'path:nth-child(99)', likely to highlight or interact with another specific data point in the chart.</t>
+        </is>
+      </c>
+      <c r="C377" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("path:nth-child(99)").click()`</t>
+        </is>
+      </c>
+      <c r="D377" s="3" t="inlineStr"/>
+      <c r="E377" s="4" t="inlineStr"/>
+      <c r="F377" s="4" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="3" t="inlineStr">
+        <is>
+          <t>.9</t>
+        </is>
+      </c>
+      <c r="B378" s="4" t="inlineStr">
+        <is>
+          <t>Click on the bar chart element corresponding to 'path:nth-child(98)', likely to highlight or interact with yet another specific data point in the chart.</t>
+        </is>
+      </c>
+      <c r="C378" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("path:nth-child(98)").click()`</t>
+        </is>
+      </c>
+      <c r="D378" s="3" t="inlineStr"/>
+      <c r="E378" s="4" t="inlineStr"/>
+      <c r="F378" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="63">
+    <mergeCell ref="A305:F305"/>
+    <mergeCell ref="A363:F363"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A246:F246"/>
+    <mergeCell ref="A255:F255"/>
+    <mergeCell ref="A282:F282"/>
+    <mergeCell ref="A164:F164"/>
+    <mergeCell ref="A273:F273"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A317:F317"/>
+    <mergeCell ref="A236:F236"/>
+    <mergeCell ref="A369:F369"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A331:F331"/>
+    <mergeCell ref="A269:F269"/>
+    <mergeCell ref="A307:F307"/>
+    <mergeCell ref="A185:F185"/>
+    <mergeCell ref="A312:F312"/>
+    <mergeCell ref="A309:F309"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A106:F106"/>
+    <mergeCell ref="A141:F141"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A131:F131"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A280:F280"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A121:F121"/>
+    <mergeCell ref="A93:F93"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A288:F288"/>
+    <mergeCell ref="A173:F173"/>
+    <mergeCell ref="A357:F357"/>
+    <mergeCell ref="A258:F258"/>
+    <mergeCell ref="A127:F127"/>
+    <mergeCell ref="A276:F276"/>
+    <mergeCell ref="A201:F201"/>
+    <mergeCell ref="A352:F352"/>
+    <mergeCell ref="A261:F261"/>
+    <mergeCell ref="A337:F337"/>
+    <mergeCell ref="A266:F266"/>
+    <mergeCell ref="A222:F222"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A291:F291"/>
+    <mergeCell ref="A169:F169"/>
+    <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A207:F207"/>
+    <mergeCell ref="A225:F225"/>
+    <mergeCell ref="A197:F197"/>
+    <mergeCell ref="A241:F241"/>
+    <mergeCell ref="A146:F146"/>
+    <mergeCell ref="A325:F325"/>
+    <mergeCell ref="A343:F343"/>
+    <mergeCell ref="A250:F250"/>
+    <mergeCell ref="A87:F87"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
